--- a/build/output/PoliceStation_v2.2_部署版.xlsx
+++ b/build/output/PoliceStation_v2.2_部署版.xlsx
@@ -1835,7 +1835,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl案件" displayName="Tbl案件" ref="A14:Y218" headerRowCount="1">
-  <autoFilter ref="A14:Y218"/>
   <tableColumns count="25">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="案類"/>
@@ -1854,13 +1853,25 @@
     <tableColumn id="15" name="涉案金額"/>
     <tableColumn id="16" name="建立日期"/>
     <tableColumn id="17" name="建立者"/>
-    <tableColumn id="18" name="是否破獲"/>
-    <tableColumn id="19" name="歸屬年度"/>
-    <tableColumn id="20" name="案類分類"/>
-    <tableColumn id="21" name="是否納入統計"/>
-    <tableColumn id="22" name="主排序鍵"/>
+    <tableColumn id="18" name="是否破獲">
+      <calculatedColumnFormula>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" name="歸屬年度">
+      <calculatedColumnFormula>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" name="案類分類">
+      <calculatedColumnFormula>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" name="是否納入統計">
+      <calculatedColumnFormula>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" name="主排序鍵">
+      <calculatedColumnFormula>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="23" name="績效類別"/>
-    <tableColumn id="24" name="計入發生數"/>
+    <tableColumn id="24" name="計入發生數">
+      <calculatedColumnFormula>IFERROR(IF([@績效類別]="","是","否"),"是")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="25" name="自填案類"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1869,7 +1880,6 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl毒調" displayName="Tbl毒調" ref="A14:N84" headerRowCount="1">
-  <autoFilter ref="A14:N84"/>
   <tableColumns count="14">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="姓名"/>
@@ -1881,10 +1891,18 @@
     <tableColumn id="8" name="管制情形"/>
     <tableColumn id="9" name="備註"/>
     <tableColumn id="10" name="最後到驗日"/>
-    <tableColumn id="11" name="距今天數"/>
-    <tableColumn id="12" name="是否到驗"/>
-    <tableColumn id="13" name="狀態燈"/>
-    <tableColumn id="14" name="候選旗標"/>
+    <tableColumn id="11" name="距今天數">
+      <calculatedColumnFormula>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" name="是否到驗">
+      <calculatedColumnFormula>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" name="狀態燈">
+      <calculatedColumnFormula>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" name="候選旗標">
+      <calculatedColumnFormula>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1892,7 +1910,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tbl交通" displayName="Tbl交通" ref="A14:F119" headerRowCount="1">
-  <autoFilter ref="A14:F119"/>
   <tableColumns count="6">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="取締日期"/>
@@ -1907,7 +1924,6 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tbl歷史" displayName="Tbl歷史" ref="A10:N45" headerRowCount="1">
-  <autoFilter ref="A10:N45"/>
   <tableColumns count="14">
     <tableColumn id="1" name="統計年月"/>
     <tableColumn id="2" name="全般發生"/>

--- a/build/output/PoliceStation_v2.2_部署版.xlsx
+++ b/build/output/PoliceStation_v2.2_部署版.xlsx
@@ -1835,6 +1835,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl案件" displayName="Tbl案件" ref="A14:Y218" headerRowCount="1">
+  <autoFilter ref="A14:Y218"/>
   <tableColumns count="25">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="案類"/>
@@ -1853,25 +1854,13 @@
     <tableColumn id="15" name="涉案金額"/>
     <tableColumn id="16" name="建立日期"/>
     <tableColumn id="17" name="建立者"/>
-    <tableColumn id="18" name="是否破獲">
-      <calculatedColumnFormula>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" name="歸屬年度">
-      <calculatedColumnFormula>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="20" name="案類分類">
-      <calculatedColumnFormula>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" name="是否納入統計">
-      <calculatedColumnFormula>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="22" name="主排序鍵">
-      <calculatedColumnFormula>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="18" name="是否破獲"/>
+    <tableColumn id="19" name="歸屬年度"/>
+    <tableColumn id="20" name="案類分類"/>
+    <tableColumn id="21" name="是否納入統計"/>
+    <tableColumn id="22" name="主排序鍵"/>
     <tableColumn id="23" name="績效類別"/>
-    <tableColumn id="24" name="計入發生數">
-      <calculatedColumnFormula>IFERROR(IF([@績效類別]="","是","否"),"是")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="24" name="計入發生數"/>
     <tableColumn id="25" name="自填案類"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1880,6 +1869,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl毒調" displayName="Tbl毒調" ref="A14:N84" headerRowCount="1">
+  <autoFilter ref="A14:N84"/>
   <tableColumns count="14">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="姓名"/>
@@ -1891,18 +1881,10 @@
     <tableColumn id="8" name="管制情形"/>
     <tableColumn id="9" name="備註"/>
     <tableColumn id="10" name="最後到驗日"/>
-    <tableColumn id="11" name="距今天數">
-      <calculatedColumnFormula>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" name="是否到驗">
-      <calculatedColumnFormula>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" name="狀態燈">
-      <calculatedColumnFormula>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" name="候選旗標">
-      <calculatedColumnFormula>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="11" name="距今天數"/>
+    <tableColumn id="12" name="是否到驗"/>
+    <tableColumn id="13" name="狀態燈"/>
+    <tableColumn id="14" name="候選旗標"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1910,6 +1892,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tbl交通" displayName="Tbl交通" ref="A14:F119" headerRowCount="1">
+  <autoFilter ref="A14:F119"/>
   <tableColumns count="6">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="取締日期"/>
@@ -1924,6 +1907,7 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tbl歷史" displayName="Tbl歷史" ref="A10:N45" headerRowCount="1">
+  <autoFilter ref="A10:N45"/>
   <tableColumns count="14">
     <tableColumn id="1" name="統計年月"/>
     <tableColumn id="2" name="全般發生"/>
@@ -25221,28 +25205,28 @@
       <c r="P15" s="226" t="n"/>
       <c r="Q15" s="223" t="n"/>
       <c r="R15" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J15="已破獲未移送",J15="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S15" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D15="","",YEAR(D15)-1911),"")</f>
         <v/>
       </c>
       <c r="T15" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B15,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U15" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B15,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V15" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S15*10000+IFERROR(MATCH(J15,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W15" s="223" t="inlineStr"/>
       <c r="X15" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W15="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y15" s="223" t="inlineStr"/>
@@ -25266,28 +25250,28 @@
       <c r="P16" s="226" t="n"/>
       <c r="Q16" s="223" t="n"/>
       <c r="R16" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J16="已破獲未移送",J16="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S16" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D16="","",YEAR(D16)-1911),"")</f>
         <v/>
       </c>
       <c r="T16" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B16,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U16" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B16,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V16" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S16*10000+IFERROR(MATCH(J16,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W16" s="223" t="inlineStr"/>
       <c r="X16" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W16="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y16" s="223" t="inlineStr"/>
@@ -25311,28 +25295,28 @@
       <c r="P17" s="226" t="n"/>
       <c r="Q17" s="223" t="n"/>
       <c r="R17" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J17="已破獲未移送",J17="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S17" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D17="","",YEAR(D17)-1911),"")</f>
         <v/>
       </c>
       <c r="T17" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B17,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U17" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B17,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V17" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S17*10000+IFERROR(MATCH(J17,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W17" s="223" t="n"/>
       <c r="X17" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W17="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y17" s="223" t="inlineStr"/>
@@ -25356,28 +25340,28 @@
       <c r="P18" s="226" t="n"/>
       <c r="Q18" s="223" t="n"/>
       <c r="R18" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J18="已破獲未移送",J18="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S18" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D18="","",YEAR(D18)-1911),"")</f>
         <v/>
       </c>
       <c r="T18" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B18,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U18" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B18,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V18" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S18*10000+IFERROR(MATCH(J18,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W18" s="223" t="n"/>
       <c r="X18" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W18="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y18" s="223" t="inlineStr"/>
@@ -25401,28 +25385,28 @@
       <c r="P19" s="230" t="n"/>
       <c r="Q19" s="227" t="n"/>
       <c r="R19" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J19="已破獲未移送",J19="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S19" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D19="","",YEAR(D19)-1911),"")</f>
         <v/>
       </c>
       <c r="T19" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B19,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U19" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B19,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V19" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S19*10000+IFERROR(MATCH(J19,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W19" s="227" t="n"/>
       <c r="X19" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W19="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y19" s="227" t="n"/>
@@ -25446,28 +25430,28 @@
       <c r="P20" s="230" t="n"/>
       <c r="Q20" s="227" t="n"/>
       <c r="R20" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J20="已破獲未移送",J20="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S20" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D20="","",YEAR(D20)-1911),"")</f>
         <v/>
       </c>
       <c r="T20" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B20,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U20" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B20,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V20" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S20*10000+IFERROR(MATCH(J20,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W20" s="227" t="n"/>
       <c r="X20" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W20="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y20" s="227" t="n"/>
@@ -25491,28 +25475,28 @@
       <c r="P21" s="230" t="n"/>
       <c r="Q21" s="227" t="n"/>
       <c r="R21" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J21="已破獲未移送",J21="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S21" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D21="","",YEAR(D21)-1911),"")</f>
         <v/>
       </c>
       <c r="T21" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B21,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U21" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B21,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V21" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S21*10000+IFERROR(MATCH(J21,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W21" s="227" t="n"/>
       <c r="X21" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W21="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y21" s="227" t="n"/>
@@ -25536,28 +25520,28 @@
       <c r="P22" s="230" t="n"/>
       <c r="Q22" s="227" t="n"/>
       <c r="R22" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J22="已破獲未移送",J22="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S22" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D22="","",YEAR(D22)-1911),"")</f>
         <v/>
       </c>
       <c r="T22" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B22,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U22" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B22,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V22" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S22*10000+IFERROR(MATCH(J22,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W22" s="227" t="n"/>
       <c r="X22" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W22="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y22" s="227" t="n"/>
@@ -25581,28 +25565,28 @@
       <c r="P23" s="230" t="n"/>
       <c r="Q23" s="227" t="n"/>
       <c r="R23" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J23="已破獲未移送",J23="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S23" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D23="","",YEAR(D23)-1911),"")</f>
         <v/>
       </c>
       <c r="T23" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B23,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U23" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B23,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V23" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S23*10000+IFERROR(MATCH(J23,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W23" s="227" t="n"/>
       <c r="X23" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W23="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y23" s="227" t="n"/>
@@ -25626,28 +25610,28 @@
       <c r="P24" s="230" t="n"/>
       <c r="Q24" s="227" t="n"/>
       <c r="R24" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J24="已破獲未移送",J24="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S24" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D24="","",YEAR(D24)-1911),"")</f>
         <v/>
       </c>
       <c r="T24" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B24,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U24" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B24,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V24" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S24*10000+IFERROR(MATCH(J24,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W24" s="227" t="n"/>
       <c r="X24" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W24="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y24" s="227" t="n"/>
@@ -25671,28 +25655,28 @@
       <c r="P25" s="230" t="n"/>
       <c r="Q25" s="227" t="n"/>
       <c r="R25" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J25="已破獲未移送",J25="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S25" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D25="","",YEAR(D25)-1911),"")</f>
         <v/>
       </c>
       <c r="T25" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B25,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U25" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B25,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V25" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S25*10000+IFERROR(MATCH(J25,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W25" s="227" t="n"/>
       <c r="X25" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W25="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y25" s="227" t="n"/>
@@ -25716,28 +25700,28 @@
       <c r="P26" s="230" t="n"/>
       <c r="Q26" s="227" t="n"/>
       <c r="R26" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J26="已破獲未移送",J26="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S26" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D26="","",YEAR(D26)-1911),"")</f>
         <v/>
       </c>
       <c r="T26" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B26,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U26" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B26,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V26" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S26*10000+IFERROR(MATCH(J26,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W26" s="227" t="n"/>
       <c r="X26" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W26="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y26" s="227" t="n"/>
@@ -25761,28 +25745,28 @@
       <c r="P27" s="230" t="n"/>
       <c r="Q27" s="227" t="n"/>
       <c r="R27" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J27="已破獲未移送",J27="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S27" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D27="","",YEAR(D27)-1911),"")</f>
         <v/>
       </c>
       <c r="T27" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B27,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U27" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B27,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V27" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S27*10000+IFERROR(MATCH(J27,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W27" s="227" t="n"/>
       <c r="X27" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W27="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y27" s="227" t="n"/>
@@ -25806,28 +25790,28 @@
       <c r="P28" s="230" t="n"/>
       <c r="Q28" s="227" t="n"/>
       <c r="R28" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J28="已破獲未移送",J28="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S28" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D28="","",YEAR(D28)-1911),"")</f>
         <v/>
       </c>
       <c r="T28" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B28,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U28" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B28,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V28" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S28*10000+IFERROR(MATCH(J28,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W28" s="227" t="n"/>
       <c r="X28" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W28="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y28" s="227" t="n"/>
@@ -25851,28 +25835,28 @@
       <c r="P29" s="230" t="n"/>
       <c r="Q29" s="227" t="n"/>
       <c r="R29" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J29="已破獲未移送",J29="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S29" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D29="","",YEAR(D29)-1911),"")</f>
         <v/>
       </c>
       <c r="T29" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B29,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U29" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B29,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V29" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S29*10000+IFERROR(MATCH(J29,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W29" s="227" t="n"/>
       <c r="X29" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W29="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y29" s="227" t="n"/>
@@ -25896,28 +25880,28 @@
       <c r="P30" s="230" t="n"/>
       <c r="Q30" s="227" t="n"/>
       <c r="R30" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J30="已破獲未移送",J30="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S30" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D30="","",YEAR(D30)-1911),"")</f>
         <v/>
       </c>
       <c r="T30" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B30,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U30" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B30,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V30" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S30*10000+IFERROR(MATCH(J30,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W30" s="227" t="n"/>
       <c r="X30" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W30="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y30" s="227" t="n"/>
@@ -25941,28 +25925,28 @@
       <c r="P31" s="230" t="n"/>
       <c r="Q31" s="227" t="n"/>
       <c r="R31" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J31="已破獲未移送",J31="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S31" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D31="","",YEAR(D31)-1911),"")</f>
         <v/>
       </c>
       <c r="T31" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B31,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U31" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B31,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V31" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S31*10000+IFERROR(MATCH(J31,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W31" s="227" t="n"/>
       <c r="X31" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W31="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y31" s="227" t="n"/>
@@ -25986,28 +25970,28 @@
       <c r="P32" s="230" t="n"/>
       <c r="Q32" s="227" t="n"/>
       <c r="R32" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J32="已破獲未移送",J32="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S32" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D32="","",YEAR(D32)-1911),"")</f>
         <v/>
       </c>
       <c r="T32" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B32,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U32" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B32,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V32" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S32*10000+IFERROR(MATCH(J32,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W32" s="227" t="n"/>
       <c r="X32" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W32="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y32" s="227" t="n"/>
@@ -26031,28 +26015,28 @@
       <c r="P33" s="230" t="n"/>
       <c r="Q33" s="227" t="n"/>
       <c r="R33" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J33="已破獲未移送",J33="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S33" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D33="","",YEAR(D33)-1911),"")</f>
         <v/>
       </c>
       <c r="T33" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B33,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U33" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B33,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V33" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S33*10000+IFERROR(MATCH(J33,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W33" s="227" t="n"/>
       <c r="X33" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W33="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y33" s="227" t="n"/>
@@ -26076,28 +26060,28 @@
       <c r="P34" s="230" t="n"/>
       <c r="Q34" s="227" t="n"/>
       <c r="R34" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J34="已破獲未移送",J34="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S34" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D34="","",YEAR(D34)-1911),"")</f>
         <v/>
       </c>
       <c r="T34" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B34,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U34" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B34,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V34" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S34*10000+IFERROR(MATCH(J34,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W34" s="227" t="n"/>
       <c r="X34" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W34="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y34" s="227" t="n"/>
@@ -26121,28 +26105,28 @@
       <c r="P35" s="230" t="n"/>
       <c r="Q35" s="227" t="n"/>
       <c r="R35" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J35="已破獲未移送",J35="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S35" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D35="","",YEAR(D35)-1911),"")</f>
         <v/>
       </c>
       <c r="T35" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B35,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U35" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B35,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V35" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S35*10000+IFERROR(MATCH(J35,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W35" s="227" t="n"/>
       <c r="X35" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W35="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y35" s="227" t="n"/>
@@ -26166,28 +26150,28 @@
       <c r="P36" s="230" t="n"/>
       <c r="Q36" s="227" t="n"/>
       <c r="R36" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J36="已破獲未移送",J36="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S36" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D36="","",YEAR(D36)-1911),"")</f>
         <v/>
       </c>
       <c r="T36" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B36,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U36" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B36,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V36" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S36*10000+IFERROR(MATCH(J36,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W36" s="227" t="n"/>
       <c r="X36" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W36="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y36" s="227" t="n"/>
@@ -26211,28 +26195,28 @@
       <c r="P37" s="230" t="n"/>
       <c r="Q37" s="227" t="n"/>
       <c r="R37" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J37="已破獲未移送",J37="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S37" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D37="","",YEAR(D37)-1911),"")</f>
         <v/>
       </c>
       <c r="T37" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B37,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U37" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B37,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V37" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S37*10000+IFERROR(MATCH(J37,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W37" s="227" t="n"/>
       <c r="X37" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W37="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y37" s="227" t="n"/>
@@ -26256,28 +26240,28 @@
       <c r="P38" s="230" t="n"/>
       <c r="Q38" s="227" t="n"/>
       <c r="R38" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J38="已破獲未移送",J38="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S38" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D38="","",YEAR(D38)-1911),"")</f>
         <v/>
       </c>
       <c r="T38" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B38,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U38" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B38,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V38" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S38*10000+IFERROR(MATCH(J38,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W38" s="227" t="n"/>
       <c r="X38" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W38="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y38" s="227" t="n"/>
@@ -26301,28 +26285,28 @@
       <c r="P39" s="230" t="n"/>
       <c r="Q39" s="227" t="n"/>
       <c r="R39" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J39="已破獲未移送",J39="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S39" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D39="","",YEAR(D39)-1911),"")</f>
         <v/>
       </c>
       <c r="T39" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B39,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U39" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B39,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V39" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S39*10000+IFERROR(MATCH(J39,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W39" s="227" t="n"/>
       <c r="X39" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W39="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y39" s="227" t="n"/>
@@ -26346,28 +26330,28 @@
       <c r="P40" s="230" t="n"/>
       <c r="Q40" s="227" t="n"/>
       <c r="R40" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J40="已破獲未移送",J40="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S40" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D40="","",YEAR(D40)-1911),"")</f>
         <v/>
       </c>
       <c r="T40" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B40,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U40" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B40,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V40" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S40*10000+IFERROR(MATCH(J40,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W40" s="227" t="n"/>
       <c r="X40" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W40="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y40" s="227" t="n"/>
@@ -26391,28 +26375,28 @@
       <c r="P41" s="230" t="n"/>
       <c r="Q41" s="227" t="n"/>
       <c r="R41" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J41="已破獲未移送",J41="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S41" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D41="","",YEAR(D41)-1911),"")</f>
         <v/>
       </c>
       <c r="T41" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B41,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U41" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B41,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V41" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S41*10000+IFERROR(MATCH(J41,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W41" s="227" t="n"/>
       <c r="X41" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W41="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y41" s="227" t="n"/>
@@ -26436,28 +26420,28 @@
       <c r="P42" s="230" t="n"/>
       <c r="Q42" s="227" t="n"/>
       <c r="R42" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J42="已破獲未移送",J42="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S42" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D42="","",YEAR(D42)-1911),"")</f>
         <v/>
       </c>
       <c r="T42" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B42,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U42" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B42,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V42" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S42*10000+IFERROR(MATCH(J42,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W42" s="227" t="n"/>
       <c r="X42" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W42="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y42" s="227" t="n"/>
@@ -26481,28 +26465,28 @@
       <c r="P43" s="230" t="n"/>
       <c r="Q43" s="227" t="n"/>
       <c r="R43" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J43="已破獲未移送",J43="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S43" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D43="","",YEAR(D43)-1911),"")</f>
         <v/>
       </c>
       <c r="T43" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B43,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U43" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B43,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V43" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S43*10000+IFERROR(MATCH(J43,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W43" s="227" t="n"/>
       <c r="X43" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W43="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y43" s="227" t="n"/>
@@ -26526,28 +26510,28 @@
       <c r="P44" s="230" t="n"/>
       <c r="Q44" s="227" t="n"/>
       <c r="R44" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J44="已破獲未移送",J44="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S44" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D44="","",YEAR(D44)-1911),"")</f>
         <v/>
       </c>
       <c r="T44" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B44,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U44" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B44,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V44" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S44*10000+IFERROR(MATCH(J44,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W44" s="227" t="n"/>
       <c r="X44" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W44="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y44" s="227" t="n"/>
@@ -26571,28 +26555,28 @@
       <c r="P45" s="230" t="n"/>
       <c r="Q45" s="227" t="n"/>
       <c r="R45" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J45="已破獲未移送",J45="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S45" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D45="","",YEAR(D45)-1911),"")</f>
         <v/>
       </c>
       <c r="T45" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B45,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U45" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B45,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V45" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S45*10000+IFERROR(MATCH(J45,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W45" s="227" t="n"/>
       <c r="X45" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W45="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y45" s="227" t="n"/>
@@ -26616,28 +26600,28 @@
       <c r="P46" s="230" t="n"/>
       <c r="Q46" s="227" t="n"/>
       <c r="R46" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J46="已破獲未移送",J46="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S46" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D46="","",YEAR(D46)-1911),"")</f>
         <v/>
       </c>
       <c r="T46" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B46,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U46" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B46,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V46" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S46*10000+IFERROR(MATCH(J46,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W46" s="227" t="n"/>
       <c r="X46" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W46="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y46" s="227" t="n"/>
@@ -26661,28 +26645,28 @@
       <c r="P47" s="230" t="n"/>
       <c r="Q47" s="227" t="n"/>
       <c r="R47" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J47="已破獲未移送",J47="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S47" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D47="","",YEAR(D47)-1911),"")</f>
         <v/>
       </c>
       <c r="T47" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B47,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U47" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B47,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V47" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S47*10000+IFERROR(MATCH(J47,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W47" s="227" t="n"/>
       <c r="X47" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W47="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y47" s="227" t="n"/>
@@ -26706,28 +26690,28 @@
       <c r="P48" s="230" t="n"/>
       <c r="Q48" s="227" t="n"/>
       <c r="R48" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J48="已破獲未移送",J48="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S48" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D48="","",YEAR(D48)-1911),"")</f>
         <v/>
       </c>
       <c r="T48" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B48,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U48" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B48,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V48" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S48*10000+IFERROR(MATCH(J48,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W48" s="227" t="n"/>
       <c r="X48" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W48="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y48" s="227" t="n"/>
@@ -26751,28 +26735,28 @@
       <c r="P49" s="230" t="n"/>
       <c r="Q49" s="227" t="n"/>
       <c r="R49" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J49="已破獲未移送",J49="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S49" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D49="","",YEAR(D49)-1911),"")</f>
         <v/>
       </c>
       <c r="T49" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B49,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U49" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B49,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V49" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S49*10000+IFERROR(MATCH(J49,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W49" s="227" t="n"/>
       <c r="X49" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W49="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y49" s="227" t="n"/>
@@ -26796,28 +26780,28 @@
       <c r="P50" s="230" t="n"/>
       <c r="Q50" s="227" t="n"/>
       <c r="R50" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J50="已破獲未移送",J50="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S50" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D50="","",YEAR(D50)-1911),"")</f>
         <v/>
       </c>
       <c r="T50" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B50,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U50" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B50,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V50" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S50*10000+IFERROR(MATCH(J50,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W50" s="227" t="n"/>
       <c r="X50" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W50="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y50" s="227" t="n"/>
@@ -26841,28 +26825,28 @@
       <c r="P51" s="230" t="n"/>
       <c r="Q51" s="227" t="n"/>
       <c r="R51" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J51="已破獲未移送",J51="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S51" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D51="","",YEAR(D51)-1911),"")</f>
         <v/>
       </c>
       <c r="T51" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B51,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U51" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B51,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V51" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S51*10000+IFERROR(MATCH(J51,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W51" s="227" t="n"/>
       <c r="X51" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W51="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y51" s="227" t="n"/>
@@ -26886,28 +26870,28 @@
       <c r="P52" s="230" t="n"/>
       <c r="Q52" s="227" t="n"/>
       <c r="R52" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J52="已破獲未移送",J52="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S52" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D52="","",YEAR(D52)-1911),"")</f>
         <v/>
       </c>
       <c r="T52" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B52,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U52" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B52,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V52" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S52*10000+IFERROR(MATCH(J52,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W52" s="227" t="n"/>
       <c r="X52" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W52="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y52" s="227" t="n"/>
@@ -26931,28 +26915,28 @@
       <c r="P53" s="230" t="n"/>
       <c r="Q53" s="227" t="n"/>
       <c r="R53" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J53="已破獲未移送",J53="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S53" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D53="","",YEAR(D53)-1911),"")</f>
         <v/>
       </c>
       <c r="T53" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B53,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U53" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B53,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V53" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S53*10000+IFERROR(MATCH(J53,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W53" s="227" t="n"/>
       <c r="X53" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W53="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y53" s="227" t="n"/>
@@ -26976,28 +26960,28 @@
       <c r="P54" s="230" t="n"/>
       <c r="Q54" s="227" t="n"/>
       <c r="R54" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J54="已破獲未移送",J54="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S54" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D54="","",YEAR(D54)-1911),"")</f>
         <v/>
       </c>
       <c r="T54" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B54,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U54" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B54,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V54" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S54*10000+IFERROR(MATCH(J54,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W54" s="227" t="n"/>
       <c r="X54" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W54="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y54" s="227" t="n"/>
@@ -27021,28 +27005,28 @@
       <c r="P55" s="230" t="n"/>
       <c r="Q55" s="227" t="n"/>
       <c r="R55" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J55="已破獲未移送",J55="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S55" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D55="","",YEAR(D55)-1911),"")</f>
         <v/>
       </c>
       <c r="T55" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B55,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U55" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B55,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V55" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S55*10000+IFERROR(MATCH(J55,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W55" s="227" t="n"/>
       <c r="X55" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W55="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y55" s="227" t="n"/>
@@ -27066,28 +27050,28 @@
       <c r="P56" s="230" t="n"/>
       <c r="Q56" s="227" t="n"/>
       <c r="R56" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J56="已破獲未移送",J56="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S56" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D56="","",YEAR(D56)-1911),"")</f>
         <v/>
       </c>
       <c r="T56" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B56,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U56" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B56,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V56" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S56*10000+IFERROR(MATCH(J56,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W56" s="227" t="n"/>
       <c r="X56" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W56="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y56" s="227" t="n"/>
@@ -27111,28 +27095,28 @@
       <c r="P57" s="230" t="n"/>
       <c r="Q57" s="227" t="n"/>
       <c r="R57" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J57="已破獲未移送",J57="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S57" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D57="","",YEAR(D57)-1911),"")</f>
         <v/>
       </c>
       <c r="T57" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B57,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U57" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B57,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V57" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S57*10000+IFERROR(MATCH(J57,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W57" s="227" t="n"/>
       <c r="X57" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W57="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y57" s="227" t="n"/>
@@ -27156,28 +27140,28 @@
       <c r="P58" s="230" t="n"/>
       <c r="Q58" s="227" t="n"/>
       <c r="R58" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J58="已破獲未移送",J58="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S58" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D58="","",YEAR(D58)-1911),"")</f>
         <v/>
       </c>
       <c r="T58" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B58,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U58" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B58,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V58" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S58*10000+IFERROR(MATCH(J58,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W58" s="227" t="n"/>
       <c r="X58" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W58="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y58" s="227" t="n"/>
@@ -27201,28 +27185,28 @@
       <c r="P59" s="230" t="n"/>
       <c r="Q59" s="227" t="n"/>
       <c r="R59" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J59="已破獲未移送",J59="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S59" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D59="","",YEAR(D59)-1911),"")</f>
         <v/>
       </c>
       <c r="T59" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B59,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U59" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B59,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V59" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S59*10000+IFERROR(MATCH(J59,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W59" s="227" t="n"/>
       <c r="X59" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W59="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y59" s="227" t="n"/>
@@ -27246,28 +27230,28 @@
       <c r="P60" s="230" t="n"/>
       <c r="Q60" s="227" t="n"/>
       <c r="R60" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J60="已破獲未移送",J60="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S60" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D60="","",YEAR(D60)-1911),"")</f>
         <v/>
       </c>
       <c r="T60" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B60,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U60" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B60,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V60" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S60*10000+IFERROR(MATCH(J60,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W60" s="227" t="n"/>
       <c r="X60" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W60="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y60" s="227" t="n"/>
@@ -27291,28 +27275,28 @@
       <c r="P61" s="230" t="n"/>
       <c r="Q61" s="227" t="n"/>
       <c r="R61" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J61="已破獲未移送",J61="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S61" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D61="","",YEAR(D61)-1911),"")</f>
         <v/>
       </c>
       <c r="T61" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B61,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U61" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B61,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V61" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S61*10000+IFERROR(MATCH(J61,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W61" s="227" t="n"/>
       <c r="X61" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W61="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y61" s="227" t="n"/>
@@ -27336,28 +27320,28 @@
       <c r="P62" s="230" t="n"/>
       <c r="Q62" s="227" t="n"/>
       <c r="R62" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J62="已破獲未移送",J62="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S62" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D62="","",YEAR(D62)-1911),"")</f>
         <v/>
       </c>
       <c r="T62" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B62,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U62" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B62,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V62" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S62*10000+IFERROR(MATCH(J62,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W62" s="227" t="n"/>
       <c r="X62" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W62="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y62" s="227" t="n"/>
@@ -27381,28 +27365,28 @@
       <c r="P63" s="230" t="n"/>
       <c r="Q63" s="227" t="n"/>
       <c r="R63" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J63="已破獲未移送",J63="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S63" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D63="","",YEAR(D63)-1911),"")</f>
         <v/>
       </c>
       <c r="T63" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B63,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U63" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B63,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V63" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S63*10000+IFERROR(MATCH(J63,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W63" s="227" t="n"/>
       <c r="X63" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W63="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y63" s="227" t="n"/>
@@ -27426,28 +27410,28 @@
       <c r="P64" s="230" t="n"/>
       <c r="Q64" s="227" t="n"/>
       <c r="R64" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J64="已破獲未移送",J64="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S64" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D64="","",YEAR(D64)-1911),"")</f>
         <v/>
       </c>
       <c r="T64" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B64,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U64" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B64,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V64" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S64*10000+IFERROR(MATCH(J64,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W64" s="227" t="n"/>
       <c r="X64" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W64="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y64" s="227" t="n"/>
@@ -27471,28 +27455,28 @@
       <c r="P65" s="230" t="n"/>
       <c r="Q65" s="227" t="n"/>
       <c r="R65" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J65="已破獲未移送",J65="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S65" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D65="","",YEAR(D65)-1911),"")</f>
         <v/>
       </c>
       <c r="T65" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B65,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U65" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B65,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V65" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S65*10000+IFERROR(MATCH(J65,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W65" s="227" t="n"/>
       <c r="X65" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W65="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y65" s="227" t="n"/>
@@ -27516,28 +27500,28 @@
       <c r="P66" s="230" t="n"/>
       <c r="Q66" s="227" t="n"/>
       <c r="R66" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J66="已破獲未移送",J66="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S66" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D66="","",YEAR(D66)-1911),"")</f>
         <v/>
       </c>
       <c r="T66" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B66,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U66" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B66,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V66" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S66*10000+IFERROR(MATCH(J66,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W66" s="227" t="n"/>
       <c r="X66" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W66="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y66" s="227" t="n"/>
@@ -27561,28 +27545,28 @@
       <c r="P67" s="230" t="n"/>
       <c r="Q67" s="227" t="n"/>
       <c r="R67" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J67="已破獲未移送",J67="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S67" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D67="","",YEAR(D67)-1911),"")</f>
         <v/>
       </c>
       <c r="T67" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B67,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U67" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B67,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V67" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S67*10000+IFERROR(MATCH(J67,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W67" s="227" t="n"/>
       <c r="X67" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W67="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y67" s="227" t="n"/>
@@ -27606,28 +27590,28 @@
       <c r="P68" s="230" t="n"/>
       <c r="Q68" s="227" t="n"/>
       <c r="R68" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J68="已破獲未移送",J68="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S68" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D68="","",YEAR(D68)-1911),"")</f>
         <v/>
       </c>
       <c r="T68" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B68,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U68" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B68,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V68" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S68*10000+IFERROR(MATCH(J68,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W68" s="227" t="n"/>
       <c r="X68" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W68="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y68" s="227" t="n"/>
@@ -27651,28 +27635,28 @@
       <c r="P69" s="230" t="n"/>
       <c r="Q69" s="227" t="n"/>
       <c r="R69" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J69="已破獲未移送",J69="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S69" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D69="","",YEAR(D69)-1911),"")</f>
         <v/>
       </c>
       <c r="T69" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B69,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U69" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B69,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V69" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S69*10000+IFERROR(MATCH(J69,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W69" s="227" t="n"/>
       <c r="X69" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W69="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y69" s="227" t="n"/>
@@ -27696,28 +27680,28 @@
       <c r="P70" s="230" t="n"/>
       <c r="Q70" s="227" t="n"/>
       <c r="R70" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J70="已破獲未移送",J70="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S70" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D70="","",YEAR(D70)-1911),"")</f>
         <v/>
       </c>
       <c r="T70" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B70,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U70" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B70,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V70" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S70*10000+IFERROR(MATCH(J70,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W70" s="227" t="n"/>
       <c r="X70" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W70="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y70" s="227" t="n"/>
@@ -27741,28 +27725,28 @@
       <c r="P71" s="230" t="n"/>
       <c r="Q71" s="227" t="n"/>
       <c r="R71" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J71="已破獲未移送",J71="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S71" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D71="","",YEAR(D71)-1911),"")</f>
         <v/>
       </c>
       <c r="T71" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B71,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U71" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B71,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V71" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S71*10000+IFERROR(MATCH(J71,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W71" s="227" t="n"/>
       <c r="X71" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W71="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y71" s="227" t="n"/>
@@ -27786,28 +27770,28 @@
       <c r="P72" s="230" t="n"/>
       <c r="Q72" s="227" t="n"/>
       <c r="R72" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J72="已破獲未移送",J72="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S72" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D72="","",YEAR(D72)-1911),"")</f>
         <v/>
       </c>
       <c r="T72" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B72,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U72" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B72,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V72" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S72*10000+IFERROR(MATCH(J72,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W72" s="227" t="n"/>
       <c r="X72" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W72="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y72" s="227" t="n"/>
@@ -27831,28 +27815,28 @@
       <c r="P73" s="230" t="n"/>
       <c r="Q73" s="227" t="n"/>
       <c r="R73" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J73="已破獲未移送",J73="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S73" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D73="","",YEAR(D73)-1911),"")</f>
         <v/>
       </c>
       <c r="T73" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B73,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U73" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B73,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V73" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S73*10000+IFERROR(MATCH(J73,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W73" s="227" t="n"/>
       <c r="X73" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W73="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y73" s="227" t="n"/>
@@ -27876,28 +27860,28 @@
       <c r="P74" s="230" t="n"/>
       <c r="Q74" s="227" t="n"/>
       <c r="R74" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J74="已破獲未移送",J74="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S74" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D74="","",YEAR(D74)-1911),"")</f>
         <v/>
       </c>
       <c r="T74" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B74,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U74" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B74,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V74" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S74*10000+IFERROR(MATCH(J74,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W74" s="227" t="n"/>
       <c r="X74" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W74="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y74" s="227" t="n"/>
@@ -27921,28 +27905,28 @@
       <c r="P75" s="230" t="n"/>
       <c r="Q75" s="227" t="n"/>
       <c r="R75" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J75="已破獲未移送",J75="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S75" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D75="","",YEAR(D75)-1911),"")</f>
         <v/>
       </c>
       <c r="T75" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B75,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U75" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B75,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V75" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S75*10000+IFERROR(MATCH(J75,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W75" s="227" t="n"/>
       <c r="X75" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W75="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y75" s="227" t="n"/>
@@ -27966,28 +27950,28 @@
       <c r="P76" s="230" t="n"/>
       <c r="Q76" s="227" t="n"/>
       <c r="R76" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J76="已破獲未移送",J76="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S76" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D76="","",YEAR(D76)-1911),"")</f>
         <v/>
       </c>
       <c r="T76" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B76,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U76" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B76,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V76" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S76*10000+IFERROR(MATCH(J76,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W76" s="227" t="n"/>
       <c r="X76" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W76="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y76" s="227" t="n"/>
@@ -28011,28 +27995,28 @@
       <c r="P77" s="230" t="n"/>
       <c r="Q77" s="227" t="n"/>
       <c r="R77" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J77="已破獲未移送",J77="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S77" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D77="","",YEAR(D77)-1911),"")</f>
         <v/>
       </c>
       <c r="T77" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B77,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U77" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B77,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V77" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S77*10000+IFERROR(MATCH(J77,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W77" s="227" t="n"/>
       <c r="X77" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W77="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y77" s="227" t="n"/>
@@ -28056,28 +28040,28 @@
       <c r="P78" s="230" t="n"/>
       <c r="Q78" s="227" t="n"/>
       <c r="R78" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J78="已破獲未移送",J78="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S78" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D78="","",YEAR(D78)-1911),"")</f>
         <v/>
       </c>
       <c r="T78" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B78,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U78" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B78,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V78" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S78*10000+IFERROR(MATCH(J78,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W78" s="227" t="n"/>
       <c r="X78" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W78="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y78" s="227" t="n"/>
@@ -28101,28 +28085,28 @@
       <c r="P79" s="230" t="n"/>
       <c r="Q79" s="227" t="n"/>
       <c r="R79" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J79="已破獲未移送",J79="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S79" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D79="","",YEAR(D79)-1911),"")</f>
         <v/>
       </c>
       <c r="T79" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B79,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U79" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B79,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V79" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S79*10000+IFERROR(MATCH(J79,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W79" s="227" t="n"/>
       <c r="X79" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W79="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y79" s="227" t="n"/>
@@ -28146,28 +28130,28 @@
       <c r="P80" s="230" t="n"/>
       <c r="Q80" s="227" t="n"/>
       <c r="R80" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J80="已破獲未移送",J80="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S80" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D80="","",YEAR(D80)-1911),"")</f>
         <v/>
       </c>
       <c r="T80" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B80,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U80" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B80,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V80" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S80*10000+IFERROR(MATCH(J80,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W80" s="227" t="n"/>
       <c r="X80" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W80="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y80" s="227" t="n"/>
@@ -28191,28 +28175,28 @@
       <c r="P81" s="230" t="n"/>
       <c r="Q81" s="227" t="n"/>
       <c r="R81" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J81="已破獲未移送",J81="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S81" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D81="","",YEAR(D81)-1911),"")</f>
         <v/>
       </c>
       <c r="T81" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B81,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U81" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B81,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V81" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S81*10000+IFERROR(MATCH(J81,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W81" s="227" t="n"/>
       <c r="X81" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W81="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y81" s="227" t="n"/>
@@ -28236,28 +28220,28 @@
       <c r="P82" s="230" t="n"/>
       <c r="Q82" s="227" t="n"/>
       <c r="R82" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J82="已破獲未移送",J82="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S82" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D82="","",YEAR(D82)-1911),"")</f>
         <v/>
       </c>
       <c r="T82" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B82,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U82" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B82,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V82" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S82*10000+IFERROR(MATCH(J82,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W82" s="227" t="n"/>
       <c r="X82" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W82="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y82" s="227" t="n"/>
@@ -28281,28 +28265,28 @@
       <c r="P83" s="230" t="n"/>
       <c r="Q83" s="227" t="n"/>
       <c r="R83" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J83="已破獲未移送",J83="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S83" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D83="","",YEAR(D83)-1911),"")</f>
         <v/>
       </c>
       <c r="T83" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B83,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U83" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B83,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V83" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S83*10000+IFERROR(MATCH(J83,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W83" s="227" t="n"/>
       <c r="X83" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W83="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y83" s="227" t="n"/>
@@ -28326,28 +28310,28 @@
       <c r="P84" s="230" t="n"/>
       <c r="Q84" s="227" t="n"/>
       <c r="R84" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J84="已破獲未移送",J84="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S84" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D84="","",YEAR(D84)-1911),"")</f>
         <v/>
       </c>
       <c r="T84" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B84,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U84" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B84,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V84" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S84*10000+IFERROR(MATCH(J84,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W84" s="227" t="n"/>
       <c r="X84" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W84="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y84" s="227" t="n"/>
@@ -28371,28 +28355,28 @@
       <c r="P85" s="230" t="n"/>
       <c r="Q85" s="227" t="n"/>
       <c r="R85" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J85="已破獲未移送",J85="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S85" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D85="","",YEAR(D85)-1911),"")</f>
         <v/>
       </c>
       <c r="T85" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B85,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U85" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B85,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V85" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S85*10000+IFERROR(MATCH(J85,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W85" s="227" t="n"/>
       <c r="X85" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W85="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y85" s="227" t="n"/>
@@ -28416,28 +28400,28 @@
       <c r="P86" s="230" t="n"/>
       <c r="Q86" s="227" t="n"/>
       <c r="R86" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J86="已破獲未移送",J86="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S86" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D86="","",YEAR(D86)-1911),"")</f>
         <v/>
       </c>
       <c r="T86" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B86,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U86" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B86,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V86" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S86*10000+IFERROR(MATCH(J86,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W86" s="227" t="n"/>
       <c r="X86" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W86="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y86" s="227" t="n"/>
@@ -28461,28 +28445,28 @@
       <c r="P87" s="230" t="n"/>
       <c r="Q87" s="227" t="n"/>
       <c r="R87" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J87="已破獲未移送",J87="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S87" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D87="","",YEAR(D87)-1911),"")</f>
         <v/>
       </c>
       <c r="T87" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B87,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U87" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B87,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V87" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S87*10000+IFERROR(MATCH(J87,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W87" s="227" t="n"/>
       <c r="X87" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W87="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y87" s="227" t="n"/>
@@ -28506,28 +28490,28 @@
       <c r="P88" s="230" t="n"/>
       <c r="Q88" s="227" t="n"/>
       <c r="R88" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J88="已破獲未移送",J88="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S88" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D88="","",YEAR(D88)-1911),"")</f>
         <v/>
       </c>
       <c r="T88" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B88,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U88" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B88,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V88" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S88*10000+IFERROR(MATCH(J88,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W88" s="227" t="n"/>
       <c r="X88" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W88="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y88" s="227" t="n"/>
@@ -28551,28 +28535,28 @@
       <c r="P89" s="230" t="n"/>
       <c r="Q89" s="227" t="n"/>
       <c r="R89" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J89="已破獲未移送",J89="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S89" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D89="","",YEAR(D89)-1911),"")</f>
         <v/>
       </c>
       <c r="T89" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B89,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U89" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B89,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V89" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S89*10000+IFERROR(MATCH(J89,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W89" s="227" t="n"/>
       <c r="X89" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W89="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y89" s="227" t="n"/>
@@ -28596,28 +28580,28 @@
       <c r="P90" s="230" t="n"/>
       <c r="Q90" s="227" t="n"/>
       <c r="R90" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J90="已破獲未移送",J90="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S90" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D90="","",YEAR(D90)-1911),"")</f>
         <v/>
       </c>
       <c r="T90" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B90,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U90" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B90,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V90" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S90*10000+IFERROR(MATCH(J90,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W90" s="227" t="n"/>
       <c r="X90" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W90="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y90" s="227" t="n"/>
@@ -28641,28 +28625,28 @@
       <c r="P91" s="230" t="n"/>
       <c r="Q91" s="227" t="n"/>
       <c r="R91" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J91="已破獲未移送",J91="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S91" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D91="","",YEAR(D91)-1911),"")</f>
         <v/>
       </c>
       <c r="T91" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B91,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U91" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B91,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V91" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S91*10000+IFERROR(MATCH(J91,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W91" s="227" t="n"/>
       <c r="X91" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W91="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y91" s="227" t="n"/>
@@ -28686,28 +28670,28 @@
       <c r="P92" s="230" t="n"/>
       <c r="Q92" s="227" t="n"/>
       <c r="R92" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J92="已破獲未移送",J92="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S92" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D92="","",YEAR(D92)-1911),"")</f>
         <v/>
       </c>
       <c r="T92" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B92,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U92" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B92,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V92" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S92*10000+IFERROR(MATCH(J92,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W92" s="227" t="n"/>
       <c r="X92" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W92="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y92" s="227" t="n"/>
@@ -28731,28 +28715,28 @@
       <c r="P93" s="230" t="n"/>
       <c r="Q93" s="227" t="n"/>
       <c r="R93" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J93="已破獲未移送",J93="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S93" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D93="","",YEAR(D93)-1911),"")</f>
         <v/>
       </c>
       <c r="T93" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B93,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U93" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B93,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V93" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S93*10000+IFERROR(MATCH(J93,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W93" s="227" t="n"/>
       <c r="X93" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W93="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y93" s="227" t="n"/>
@@ -28776,28 +28760,28 @@
       <c r="P94" s="230" t="n"/>
       <c r="Q94" s="227" t="n"/>
       <c r="R94" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J94="已破獲未移送",J94="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S94" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D94="","",YEAR(D94)-1911),"")</f>
         <v/>
       </c>
       <c r="T94" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B94,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U94" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B94,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V94" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S94*10000+IFERROR(MATCH(J94,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W94" s="227" t="n"/>
       <c r="X94" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W94="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y94" s="227" t="n"/>
@@ -28821,28 +28805,28 @@
       <c r="P95" s="230" t="n"/>
       <c r="Q95" s="227" t="n"/>
       <c r="R95" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J95="已破獲未移送",J95="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S95" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D95="","",YEAR(D95)-1911),"")</f>
         <v/>
       </c>
       <c r="T95" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B95,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U95" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B95,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V95" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S95*10000+IFERROR(MATCH(J95,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W95" s="227" t="n"/>
       <c r="X95" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W95="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y95" s="227" t="n"/>
@@ -28866,28 +28850,28 @@
       <c r="P96" s="230" t="n"/>
       <c r="Q96" s="227" t="n"/>
       <c r="R96" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J96="已破獲未移送",J96="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S96" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D96="","",YEAR(D96)-1911),"")</f>
         <v/>
       </c>
       <c r="T96" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B96,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U96" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B96,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V96" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S96*10000+IFERROR(MATCH(J96,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W96" s="227" t="n"/>
       <c r="X96" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W96="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y96" s="227" t="n"/>
@@ -28911,28 +28895,28 @@
       <c r="P97" s="230" t="n"/>
       <c r="Q97" s="227" t="n"/>
       <c r="R97" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J97="已破獲未移送",J97="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S97" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D97="","",YEAR(D97)-1911),"")</f>
         <v/>
       </c>
       <c r="T97" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B97,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U97" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B97,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V97" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S97*10000+IFERROR(MATCH(J97,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W97" s="227" t="n"/>
       <c r="X97" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W97="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y97" s="227" t="n"/>
@@ -28956,28 +28940,28 @@
       <c r="P98" s="230" t="n"/>
       <c r="Q98" s="227" t="n"/>
       <c r="R98" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J98="已破獲未移送",J98="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S98" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D98="","",YEAR(D98)-1911),"")</f>
         <v/>
       </c>
       <c r="T98" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B98,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U98" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B98,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V98" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S98*10000+IFERROR(MATCH(J98,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W98" s="227" t="n"/>
       <c r="X98" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W98="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y98" s="227" t="n"/>
@@ -29001,28 +28985,28 @@
       <c r="P99" s="230" t="n"/>
       <c r="Q99" s="227" t="n"/>
       <c r="R99" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J99="已破獲未移送",J99="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S99" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D99="","",YEAR(D99)-1911),"")</f>
         <v/>
       </c>
       <c r="T99" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B99,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U99" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B99,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V99" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S99*10000+IFERROR(MATCH(J99,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W99" s="227" t="n"/>
       <c r="X99" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W99="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y99" s="227" t="n"/>
@@ -29046,28 +29030,28 @@
       <c r="P100" s="230" t="n"/>
       <c r="Q100" s="227" t="n"/>
       <c r="R100" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J100="已破獲未移送",J100="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S100" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D100="","",YEAR(D100)-1911),"")</f>
         <v/>
       </c>
       <c r="T100" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B100,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U100" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B100,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V100" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S100*10000+IFERROR(MATCH(J100,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W100" s="227" t="n"/>
       <c r="X100" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W100="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y100" s="227" t="n"/>
@@ -29091,28 +29075,28 @@
       <c r="P101" s="230" t="n"/>
       <c r="Q101" s="227" t="n"/>
       <c r="R101" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J101="已破獲未移送",J101="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S101" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D101="","",YEAR(D101)-1911),"")</f>
         <v/>
       </c>
       <c r="T101" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B101,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U101" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B101,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V101" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S101*10000+IFERROR(MATCH(J101,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W101" s="227" t="n"/>
       <c r="X101" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W101="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y101" s="227" t="n"/>
@@ -29136,28 +29120,28 @@
       <c r="P102" s="230" t="n"/>
       <c r="Q102" s="227" t="n"/>
       <c r="R102" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J102="已破獲未移送",J102="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S102" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D102="","",YEAR(D102)-1911),"")</f>
         <v/>
       </c>
       <c r="T102" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B102,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U102" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B102,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V102" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S102*10000+IFERROR(MATCH(J102,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W102" s="227" t="n"/>
       <c r="X102" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W102="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y102" s="227" t="n"/>
@@ -29181,28 +29165,28 @@
       <c r="P103" s="230" t="n"/>
       <c r="Q103" s="227" t="n"/>
       <c r="R103" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J103="已破獲未移送",J103="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S103" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D103="","",YEAR(D103)-1911),"")</f>
         <v/>
       </c>
       <c r="T103" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B103,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U103" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B103,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V103" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S103*10000+IFERROR(MATCH(J103,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W103" s="227" t="n"/>
       <c r="X103" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W103="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y103" s="227" t="n"/>
@@ -29226,28 +29210,28 @@
       <c r="P104" s="230" t="n"/>
       <c r="Q104" s="227" t="n"/>
       <c r="R104" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J104="已破獲未移送",J104="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S104" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D104="","",YEAR(D104)-1911),"")</f>
         <v/>
       </c>
       <c r="T104" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B104,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U104" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B104,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V104" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S104*10000+IFERROR(MATCH(J104,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W104" s="227" t="n"/>
       <c r="X104" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W104="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y104" s="227" t="n"/>
@@ -29271,28 +29255,28 @@
       <c r="P105" s="230" t="n"/>
       <c r="Q105" s="227" t="n"/>
       <c r="R105" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J105="已破獲未移送",J105="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S105" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D105="","",YEAR(D105)-1911),"")</f>
         <v/>
       </c>
       <c r="T105" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B105,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U105" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B105,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V105" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S105*10000+IFERROR(MATCH(J105,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W105" s="227" t="n"/>
       <c r="X105" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W105="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y105" s="227" t="n"/>
@@ -29316,28 +29300,28 @@
       <c r="P106" s="230" t="n"/>
       <c r="Q106" s="227" t="n"/>
       <c r="R106" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J106="已破獲未移送",J106="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S106" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D106="","",YEAR(D106)-1911),"")</f>
         <v/>
       </c>
       <c r="T106" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B106,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U106" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B106,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V106" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S106*10000+IFERROR(MATCH(J106,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W106" s="227" t="n"/>
       <c r="X106" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W106="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y106" s="227" t="n"/>
@@ -29361,28 +29345,28 @@
       <c r="P107" s="230" t="n"/>
       <c r="Q107" s="227" t="n"/>
       <c r="R107" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J107="已破獲未移送",J107="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S107" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D107="","",YEAR(D107)-1911),"")</f>
         <v/>
       </c>
       <c r="T107" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B107,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U107" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B107,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V107" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S107*10000+IFERROR(MATCH(J107,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W107" s="227" t="n"/>
       <c r="X107" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W107="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y107" s="227" t="n"/>
@@ -29406,28 +29390,28 @@
       <c r="P108" s="230" t="n"/>
       <c r="Q108" s="227" t="n"/>
       <c r="R108" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J108="已破獲未移送",J108="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S108" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D108="","",YEAR(D108)-1911),"")</f>
         <v/>
       </c>
       <c r="T108" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B108,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U108" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B108,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V108" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S108*10000+IFERROR(MATCH(J108,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W108" s="227" t="n"/>
       <c r="X108" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W108="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y108" s="227" t="n"/>
@@ -29451,28 +29435,28 @@
       <c r="P109" s="230" t="n"/>
       <c r="Q109" s="227" t="n"/>
       <c r="R109" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J109="已破獲未移送",J109="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S109" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D109="","",YEAR(D109)-1911),"")</f>
         <v/>
       </c>
       <c r="T109" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B109,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U109" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B109,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V109" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S109*10000+IFERROR(MATCH(J109,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W109" s="227" t="n"/>
       <c r="X109" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W109="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y109" s="227" t="n"/>
@@ -29496,28 +29480,28 @@
       <c r="P110" s="230" t="n"/>
       <c r="Q110" s="227" t="n"/>
       <c r="R110" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J110="已破獲未移送",J110="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S110" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D110="","",YEAR(D110)-1911),"")</f>
         <v/>
       </c>
       <c r="T110" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B110,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U110" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B110,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V110" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S110*10000+IFERROR(MATCH(J110,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W110" s="227" t="n"/>
       <c r="X110" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W110="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y110" s="227" t="n"/>
@@ -29541,28 +29525,28 @@
       <c r="P111" s="230" t="n"/>
       <c r="Q111" s="227" t="n"/>
       <c r="R111" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J111="已破獲未移送",J111="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S111" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D111="","",YEAR(D111)-1911),"")</f>
         <v/>
       </c>
       <c r="T111" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B111,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U111" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B111,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V111" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S111*10000+IFERROR(MATCH(J111,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W111" s="227" t="n"/>
       <c r="X111" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W111="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y111" s="227" t="n"/>
@@ -29586,28 +29570,28 @@
       <c r="P112" s="230" t="n"/>
       <c r="Q112" s="227" t="n"/>
       <c r="R112" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J112="已破獲未移送",J112="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S112" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D112="","",YEAR(D112)-1911),"")</f>
         <v/>
       </c>
       <c r="T112" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B112,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U112" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B112,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V112" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S112*10000+IFERROR(MATCH(J112,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W112" s="227" t="n"/>
       <c r="X112" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W112="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y112" s="227" t="n"/>
@@ -29631,28 +29615,28 @@
       <c r="P113" s="230" t="n"/>
       <c r="Q113" s="227" t="n"/>
       <c r="R113" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J113="已破獲未移送",J113="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S113" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D113="","",YEAR(D113)-1911),"")</f>
         <v/>
       </c>
       <c r="T113" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B113,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U113" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B113,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V113" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S113*10000+IFERROR(MATCH(J113,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W113" s="227" t="n"/>
       <c r="X113" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W113="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y113" s="227" t="n"/>
@@ -29676,28 +29660,28 @@
       <c r="P114" s="230" t="n"/>
       <c r="Q114" s="227" t="n"/>
       <c r="R114" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J114="已破獲未移送",J114="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S114" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D114="","",YEAR(D114)-1911),"")</f>
         <v/>
       </c>
       <c r="T114" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B114,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U114" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B114,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V114" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S114*10000+IFERROR(MATCH(J114,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W114" s="227" t="n"/>
       <c r="X114" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W114="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y114" s="227" t="n"/>
@@ -29721,28 +29705,28 @@
       <c r="P115" s="230" t="n"/>
       <c r="Q115" s="227" t="n"/>
       <c r="R115" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J115="已破獲未移送",J115="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S115" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D115="","",YEAR(D115)-1911),"")</f>
         <v/>
       </c>
       <c r="T115" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B115,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U115" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B115,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V115" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S115*10000+IFERROR(MATCH(J115,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W115" s="227" t="n"/>
       <c r="X115" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W115="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y115" s="227" t="n"/>
@@ -29766,28 +29750,28 @@
       <c r="P116" s="230" t="n"/>
       <c r="Q116" s="227" t="n"/>
       <c r="R116" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J116="已破獲未移送",J116="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S116" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D116="","",YEAR(D116)-1911),"")</f>
         <v/>
       </c>
       <c r="T116" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B116,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U116" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B116,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V116" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S116*10000+IFERROR(MATCH(J116,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W116" s="227" t="n"/>
       <c r="X116" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W116="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y116" s="227" t="n"/>
@@ -29811,28 +29795,28 @@
       <c r="P117" s="230" t="n"/>
       <c r="Q117" s="227" t="n"/>
       <c r="R117" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J117="已破獲未移送",J117="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S117" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D117="","",YEAR(D117)-1911),"")</f>
         <v/>
       </c>
       <c r="T117" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B117,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U117" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B117,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V117" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S117*10000+IFERROR(MATCH(J117,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W117" s="227" t="n"/>
       <c r="X117" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W117="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y117" s="227" t="n"/>
@@ -29856,28 +29840,28 @@
       <c r="P118" s="230" t="n"/>
       <c r="Q118" s="227" t="n"/>
       <c r="R118" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J118="已破獲未移送",J118="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S118" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D118="","",YEAR(D118)-1911),"")</f>
         <v/>
       </c>
       <c r="T118" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B118,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U118" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B118,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V118" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S118*10000+IFERROR(MATCH(J118,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W118" s="227" t="n"/>
       <c r="X118" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W118="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y118" s="227" t="n"/>
@@ -29901,28 +29885,28 @@
       <c r="P119" s="230" t="n"/>
       <c r="Q119" s="227" t="n"/>
       <c r="R119" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J119="已破獲未移送",J119="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S119" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D119="","",YEAR(D119)-1911),"")</f>
         <v/>
       </c>
       <c r="T119" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B119,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U119" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B119,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V119" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S119*10000+IFERROR(MATCH(J119,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W119" s="227" t="n"/>
       <c r="X119" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W119="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y119" s="227" t="n"/>
@@ -29946,28 +29930,28 @@
       <c r="P120" s="230" t="n"/>
       <c r="Q120" s="227" t="n"/>
       <c r="R120" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J120="已破獲未移送",J120="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S120" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D120="","",YEAR(D120)-1911),"")</f>
         <v/>
       </c>
       <c r="T120" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B120,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U120" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B120,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V120" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S120*10000+IFERROR(MATCH(J120,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W120" s="227" t="n"/>
       <c r="X120" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W120="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y120" s="227" t="n"/>
@@ -29991,28 +29975,28 @@
       <c r="P121" s="230" t="n"/>
       <c r="Q121" s="227" t="n"/>
       <c r="R121" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J121="已破獲未移送",J121="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S121" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D121="","",YEAR(D121)-1911),"")</f>
         <v/>
       </c>
       <c r="T121" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B121,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U121" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B121,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V121" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S121*10000+IFERROR(MATCH(J121,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W121" s="227" t="n"/>
       <c r="X121" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W121="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y121" s="227" t="n"/>
@@ -30036,28 +30020,28 @@
       <c r="P122" s="230" t="n"/>
       <c r="Q122" s="227" t="n"/>
       <c r="R122" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J122="已破獲未移送",J122="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S122" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D122="","",YEAR(D122)-1911),"")</f>
         <v/>
       </c>
       <c r="T122" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B122,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U122" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B122,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V122" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S122*10000+IFERROR(MATCH(J122,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W122" s="227" t="n"/>
       <c r="X122" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W122="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y122" s="227" t="n"/>
@@ -30081,28 +30065,28 @@
       <c r="P123" s="230" t="n"/>
       <c r="Q123" s="227" t="n"/>
       <c r="R123" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J123="已破獲未移送",J123="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S123" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D123="","",YEAR(D123)-1911),"")</f>
         <v/>
       </c>
       <c r="T123" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B123,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U123" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B123,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V123" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S123*10000+IFERROR(MATCH(J123,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W123" s="227" t="n"/>
       <c r="X123" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W123="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y123" s="227" t="n"/>
@@ -30126,28 +30110,28 @@
       <c r="P124" s="230" t="n"/>
       <c r="Q124" s="227" t="n"/>
       <c r="R124" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J124="已破獲未移送",J124="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S124" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D124="","",YEAR(D124)-1911),"")</f>
         <v/>
       </c>
       <c r="T124" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B124,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U124" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B124,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V124" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S124*10000+IFERROR(MATCH(J124,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W124" s="227" t="n"/>
       <c r="X124" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W124="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y124" s="227" t="n"/>
@@ -30171,28 +30155,28 @@
       <c r="P125" s="230" t="n"/>
       <c r="Q125" s="227" t="n"/>
       <c r="R125" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J125="已破獲未移送",J125="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S125" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D125="","",YEAR(D125)-1911),"")</f>
         <v/>
       </c>
       <c r="T125" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B125,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U125" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B125,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V125" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S125*10000+IFERROR(MATCH(J125,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W125" s="227" t="n"/>
       <c r="X125" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W125="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y125" s="227" t="n"/>
@@ -30216,28 +30200,28 @@
       <c r="P126" s="230" t="n"/>
       <c r="Q126" s="227" t="n"/>
       <c r="R126" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J126="已破獲未移送",J126="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S126" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D126="","",YEAR(D126)-1911),"")</f>
         <v/>
       </c>
       <c r="T126" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B126,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U126" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B126,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V126" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S126*10000+IFERROR(MATCH(J126,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W126" s="227" t="n"/>
       <c r="X126" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W126="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y126" s="227" t="n"/>
@@ -30261,28 +30245,28 @@
       <c r="P127" s="230" t="n"/>
       <c r="Q127" s="227" t="n"/>
       <c r="R127" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J127="已破獲未移送",J127="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S127" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D127="","",YEAR(D127)-1911),"")</f>
         <v/>
       </c>
       <c r="T127" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B127,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U127" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B127,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V127" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S127*10000+IFERROR(MATCH(J127,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W127" s="227" t="n"/>
       <c r="X127" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W127="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y127" s="227" t="n"/>
@@ -30306,28 +30290,28 @@
       <c r="P128" s="230" t="n"/>
       <c r="Q128" s="227" t="n"/>
       <c r="R128" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J128="已破獲未移送",J128="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S128" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D128="","",YEAR(D128)-1911),"")</f>
         <v/>
       </c>
       <c r="T128" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B128,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U128" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B128,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V128" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S128*10000+IFERROR(MATCH(J128,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W128" s="227" t="n"/>
       <c r="X128" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W128="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y128" s="227" t="n"/>
@@ -30351,28 +30335,28 @@
       <c r="P129" s="230" t="n"/>
       <c r="Q129" s="227" t="n"/>
       <c r="R129" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J129="已破獲未移送",J129="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S129" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D129="","",YEAR(D129)-1911),"")</f>
         <v/>
       </c>
       <c r="T129" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B129,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U129" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B129,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V129" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S129*10000+IFERROR(MATCH(J129,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W129" s="227" t="n"/>
       <c r="X129" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W129="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y129" s="227" t="n"/>
@@ -30396,28 +30380,28 @@
       <c r="P130" s="230" t="n"/>
       <c r="Q130" s="227" t="n"/>
       <c r="R130" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J130="已破獲未移送",J130="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S130" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D130="","",YEAR(D130)-1911),"")</f>
         <v/>
       </c>
       <c r="T130" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B130,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U130" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B130,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V130" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S130*10000+IFERROR(MATCH(J130,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W130" s="227" t="n"/>
       <c r="X130" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W130="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y130" s="227" t="n"/>
@@ -30441,28 +30425,28 @@
       <c r="P131" s="230" t="n"/>
       <c r="Q131" s="227" t="n"/>
       <c r="R131" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J131="已破獲未移送",J131="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S131" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D131="","",YEAR(D131)-1911),"")</f>
         <v/>
       </c>
       <c r="T131" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B131,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U131" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B131,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V131" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S131*10000+IFERROR(MATCH(J131,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W131" s="227" t="n"/>
       <c r="X131" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W131="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y131" s="227" t="n"/>
@@ -30486,28 +30470,28 @@
       <c r="P132" s="230" t="n"/>
       <c r="Q132" s="227" t="n"/>
       <c r="R132" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J132="已破獲未移送",J132="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S132" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D132="","",YEAR(D132)-1911),"")</f>
         <v/>
       </c>
       <c r="T132" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B132,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U132" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B132,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V132" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S132*10000+IFERROR(MATCH(J132,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W132" s="227" t="n"/>
       <c r="X132" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W132="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y132" s="227" t="n"/>
@@ -30531,28 +30515,28 @@
       <c r="P133" s="230" t="n"/>
       <c r="Q133" s="227" t="n"/>
       <c r="R133" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J133="已破獲未移送",J133="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S133" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D133="","",YEAR(D133)-1911),"")</f>
         <v/>
       </c>
       <c r="T133" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B133,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U133" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B133,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V133" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S133*10000+IFERROR(MATCH(J133,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W133" s="227" t="n"/>
       <c r="X133" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W133="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y133" s="227" t="n"/>
@@ -30576,28 +30560,28 @@
       <c r="P134" s="230" t="n"/>
       <c r="Q134" s="227" t="n"/>
       <c r="R134" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J134="已破獲未移送",J134="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S134" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D134="","",YEAR(D134)-1911),"")</f>
         <v/>
       </c>
       <c r="T134" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B134,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U134" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B134,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V134" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S134*10000+IFERROR(MATCH(J134,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W134" s="227" t="n"/>
       <c r="X134" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W134="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y134" s="227" t="n"/>
@@ -30621,28 +30605,28 @@
       <c r="P135" s="230" t="n"/>
       <c r="Q135" s="227" t="n"/>
       <c r="R135" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J135="已破獲未移送",J135="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S135" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D135="","",YEAR(D135)-1911),"")</f>
         <v/>
       </c>
       <c r="T135" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B135,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U135" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B135,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V135" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S135*10000+IFERROR(MATCH(J135,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W135" s="227" t="n"/>
       <c r="X135" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W135="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y135" s="227" t="n"/>
@@ -30666,28 +30650,28 @@
       <c r="P136" s="230" t="n"/>
       <c r="Q136" s="227" t="n"/>
       <c r="R136" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J136="已破獲未移送",J136="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S136" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D136="","",YEAR(D136)-1911),"")</f>
         <v/>
       </c>
       <c r="T136" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B136,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U136" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B136,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V136" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S136*10000+IFERROR(MATCH(J136,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W136" s="227" t="n"/>
       <c r="X136" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W136="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y136" s="227" t="n"/>
@@ -30711,28 +30695,28 @@
       <c r="P137" s="230" t="n"/>
       <c r="Q137" s="227" t="n"/>
       <c r="R137" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J137="已破獲未移送",J137="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S137" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D137="","",YEAR(D137)-1911),"")</f>
         <v/>
       </c>
       <c r="T137" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B137,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U137" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B137,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V137" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S137*10000+IFERROR(MATCH(J137,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W137" s="227" t="n"/>
       <c r="X137" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W137="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y137" s="227" t="n"/>
@@ -30756,28 +30740,28 @@
       <c r="P138" s="230" t="n"/>
       <c r="Q138" s="227" t="n"/>
       <c r="R138" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J138="已破獲未移送",J138="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S138" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D138="","",YEAR(D138)-1911),"")</f>
         <v/>
       </c>
       <c r="T138" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B138,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U138" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B138,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V138" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S138*10000+IFERROR(MATCH(J138,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W138" s="227" t="n"/>
       <c r="X138" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W138="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y138" s="227" t="n"/>
@@ -30801,28 +30785,28 @@
       <c r="P139" s="230" t="n"/>
       <c r="Q139" s="227" t="n"/>
       <c r="R139" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J139="已破獲未移送",J139="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S139" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D139="","",YEAR(D139)-1911),"")</f>
         <v/>
       </c>
       <c r="T139" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B139,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U139" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B139,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V139" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S139*10000+IFERROR(MATCH(J139,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W139" s="227" t="n"/>
       <c r="X139" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W139="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y139" s="227" t="n"/>
@@ -30846,28 +30830,28 @@
       <c r="P140" s="230" t="n"/>
       <c r="Q140" s="227" t="n"/>
       <c r="R140" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J140="已破獲未移送",J140="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S140" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D140="","",YEAR(D140)-1911),"")</f>
         <v/>
       </c>
       <c r="T140" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B140,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U140" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B140,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V140" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S140*10000+IFERROR(MATCH(J140,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W140" s="227" t="n"/>
       <c r="X140" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W140="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y140" s="227" t="n"/>
@@ -30891,28 +30875,28 @@
       <c r="P141" s="230" t="n"/>
       <c r="Q141" s="227" t="n"/>
       <c r="R141" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J141="已破獲未移送",J141="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S141" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D141="","",YEAR(D141)-1911),"")</f>
         <v/>
       </c>
       <c r="T141" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B141,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U141" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B141,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V141" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S141*10000+IFERROR(MATCH(J141,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W141" s="227" t="n"/>
       <c r="X141" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W141="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y141" s="227" t="n"/>
@@ -30936,28 +30920,28 @@
       <c r="P142" s="230" t="n"/>
       <c r="Q142" s="227" t="n"/>
       <c r="R142" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J142="已破獲未移送",J142="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S142" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D142="","",YEAR(D142)-1911),"")</f>
         <v/>
       </c>
       <c r="T142" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B142,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U142" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B142,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V142" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S142*10000+IFERROR(MATCH(J142,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W142" s="227" t="n"/>
       <c r="X142" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W142="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y142" s="227" t="n"/>
@@ -30981,28 +30965,28 @@
       <c r="P143" s="230" t="n"/>
       <c r="Q143" s="227" t="n"/>
       <c r="R143" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J143="已破獲未移送",J143="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S143" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D143="","",YEAR(D143)-1911),"")</f>
         <v/>
       </c>
       <c r="T143" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B143,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U143" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B143,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V143" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S143*10000+IFERROR(MATCH(J143,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W143" s="227" t="n"/>
       <c r="X143" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W143="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y143" s="227" t="n"/>
@@ -31026,28 +31010,28 @@
       <c r="P144" s="230" t="n"/>
       <c r="Q144" s="227" t="n"/>
       <c r="R144" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J144="已破獲未移送",J144="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S144" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D144="","",YEAR(D144)-1911),"")</f>
         <v/>
       </c>
       <c r="T144" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B144,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U144" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B144,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V144" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S144*10000+IFERROR(MATCH(J144,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W144" s="227" t="n"/>
       <c r="X144" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W144="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y144" s="227" t="n"/>
@@ -31071,28 +31055,28 @@
       <c r="P145" s="230" t="n"/>
       <c r="Q145" s="227" t="n"/>
       <c r="R145" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J145="已破獲未移送",J145="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S145" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D145="","",YEAR(D145)-1911),"")</f>
         <v/>
       </c>
       <c r="T145" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B145,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U145" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B145,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V145" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S145*10000+IFERROR(MATCH(J145,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W145" s="227" t="n"/>
       <c r="X145" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W145="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y145" s="227" t="n"/>
@@ -31116,28 +31100,28 @@
       <c r="P146" s="230" t="n"/>
       <c r="Q146" s="227" t="n"/>
       <c r="R146" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J146="已破獲未移送",J146="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S146" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D146="","",YEAR(D146)-1911),"")</f>
         <v/>
       </c>
       <c r="T146" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B146,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U146" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B146,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V146" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S146*10000+IFERROR(MATCH(J146,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W146" s="227" t="n"/>
       <c r="X146" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W146="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y146" s="227" t="n"/>
@@ -31161,28 +31145,28 @@
       <c r="P147" s="230" t="n"/>
       <c r="Q147" s="227" t="n"/>
       <c r="R147" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J147="已破獲未移送",J147="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S147" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D147="","",YEAR(D147)-1911),"")</f>
         <v/>
       </c>
       <c r="T147" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B147,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U147" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B147,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V147" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S147*10000+IFERROR(MATCH(J147,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W147" s="227" t="n"/>
       <c r="X147" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W147="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y147" s="227" t="n"/>
@@ -31206,28 +31190,28 @@
       <c r="P148" s="230" t="n"/>
       <c r="Q148" s="227" t="n"/>
       <c r="R148" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J148="已破獲未移送",J148="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S148" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D148="","",YEAR(D148)-1911),"")</f>
         <v/>
       </c>
       <c r="T148" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B148,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U148" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B148,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V148" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S148*10000+IFERROR(MATCH(J148,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W148" s="227" t="n"/>
       <c r="X148" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W148="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y148" s="227" t="n"/>
@@ -31251,28 +31235,28 @@
       <c r="P149" s="230" t="n"/>
       <c r="Q149" s="227" t="n"/>
       <c r="R149" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J149="已破獲未移送",J149="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S149" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D149="","",YEAR(D149)-1911),"")</f>
         <v/>
       </c>
       <c r="T149" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B149,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U149" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B149,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V149" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S149*10000+IFERROR(MATCH(J149,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W149" s="227" t="n"/>
       <c r="X149" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W149="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y149" s="227" t="n"/>
@@ -31296,28 +31280,28 @@
       <c r="P150" s="230" t="n"/>
       <c r="Q150" s="227" t="n"/>
       <c r="R150" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J150="已破獲未移送",J150="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S150" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D150="","",YEAR(D150)-1911),"")</f>
         <v/>
       </c>
       <c r="T150" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B150,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U150" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B150,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V150" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S150*10000+IFERROR(MATCH(J150,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W150" s="227" t="n"/>
       <c r="X150" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W150="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y150" s="227" t="n"/>
@@ -31341,28 +31325,28 @@
       <c r="P151" s="230" t="n"/>
       <c r="Q151" s="227" t="n"/>
       <c r="R151" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J151="已破獲未移送",J151="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S151" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D151="","",YEAR(D151)-1911),"")</f>
         <v/>
       </c>
       <c r="T151" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B151,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U151" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B151,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V151" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S151*10000+IFERROR(MATCH(J151,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W151" s="227" t="n"/>
       <c r="X151" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W151="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y151" s="227" t="n"/>
@@ -31386,28 +31370,28 @@
       <c r="P152" s="230" t="n"/>
       <c r="Q152" s="227" t="n"/>
       <c r="R152" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J152="已破獲未移送",J152="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S152" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D152="","",YEAR(D152)-1911),"")</f>
         <v/>
       </c>
       <c r="T152" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B152,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U152" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B152,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V152" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S152*10000+IFERROR(MATCH(J152,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W152" s="227" t="n"/>
       <c r="X152" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W152="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y152" s="227" t="n"/>
@@ -31431,28 +31415,28 @@
       <c r="P153" s="230" t="n"/>
       <c r="Q153" s="227" t="n"/>
       <c r="R153" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J153="已破獲未移送",J153="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S153" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D153="","",YEAR(D153)-1911),"")</f>
         <v/>
       </c>
       <c r="T153" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B153,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U153" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B153,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V153" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S153*10000+IFERROR(MATCH(J153,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W153" s="227" t="n"/>
       <c r="X153" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W153="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y153" s="227" t="n"/>
@@ -31476,28 +31460,28 @@
       <c r="P154" s="230" t="n"/>
       <c r="Q154" s="227" t="n"/>
       <c r="R154" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J154="已破獲未移送",J154="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S154" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D154="","",YEAR(D154)-1911),"")</f>
         <v/>
       </c>
       <c r="T154" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B154,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U154" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B154,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V154" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S154*10000+IFERROR(MATCH(J154,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W154" s="227" t="n"/>
       <c r="X154" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W154="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y154" s="227" t="n"/>
@@ -31521,28 +31505,28 @@
       <c r="P155" s="230" t="n"/>
       <c r="Q155" s="227" t="n"/>
       <c r="R155" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J155="已破獲未移送",J155="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S155" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D155="","",YEAR(D155)-1911),"")</f>
         <v/>
       </c>
       <c r="T155" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B155,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U155" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B155,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V155" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S155*10000+IFERROR(MATCH(J155,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W155" s="227" t="n"/>
       <c r="X155" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W155="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y155" s="227" t="n"/>
@@ -31566,28 +31550,28 @@
       <c r="P156" s="230" t="n"/>
       <c r="Q156" s="227" t="n"/>
       <c r="R156" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J156="已破獲未移送",J156="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S156" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D156="","",YEAR(D156)-1911),"")</f>
         <v/>
       </c>
       <c r="T156" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B156,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U156" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B156,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V156" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S156*10000+IFERROR(MATCH(J156,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W156" s="227" t="n"/>
       <c r="X156" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W156="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y156" s="227" t="n"/>
@@ -31611,28 +31595,28 @@
       <c r="P157" s="230" t="n"/>
       <c r="Q157" s="227" t="n"/>
       <c r="R157" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J157="已破獲未移送",J157="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S157" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D157="","",YEAR(D157)-1911),"")</f>
         <v/>
       </c>
       <c r="T157" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B157,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U157" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B157,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V157" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S157*10000+IFERROR(MATCH(J157,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W157" s="227" t="n"/>
       <c r="X157" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W157="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y157" s="227" t="n"/>
@@ -31656,28 +31640,28 @@
       <c r="P158" s="230" t="n"/>
       <c r="Q158" s="227" t="n"/>
       <c r="R158" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J158="已破獲未移送",J158="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S158" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D158="","",YEAR(D158)-1911),"")</f>
         <v/>
       </c>
       <c r="T158" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B158,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U158" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B158,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V158" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S158*10000+IFERROR(MATCH(J158,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W158" s="227" t="n"/>
       <c r="X158" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W158="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y158" s="227" t="n"/>
@@ -31701,28 +31685,28 @@
       <c r="P159" s="230" t="n"/>
       <c r="Q159" s="227" t="n"/>
       <c r="R159" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J159="已破獲未移送",J159="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S159" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D159="","",YEAR(D159)-1911),"")</f>
         <v/>
       </c>
       <c r="T159" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B159,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U159" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B159,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V159" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S159*10000+IFERROR(MATCH(J159,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W159" s="227" t="n"/>
       <c r="X159" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W159="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y159" s="227" t="n"/>
@@ -31746,28 +31730,28 @@
       <c r="P160" s="230" t="n"/>
       <c r="Q160" s="227" t="n"/>
       <c r="R160" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J160="已破獲未移送",J160="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S160" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D160="","",YEAR(D160)-1911),"")</f>
         <v/>
       </c>
       <c r="T160" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B160,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U160" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B160,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V160" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S160*10000+IFERROR(MATCH(J160,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W160" s="227" t="n"/>
       <c r="X160" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W160="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y160" s="227" t="n"/>
@@ -31791,28 +31775,28 @@
       <c r="P161" s="230" t="n"/>
       <c r="Q161" s="227" t="n"/>
       <c r="R161" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J161="已破獲未移送",J161="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S161" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D161="","",YEAR(D161)-1911),"")</f>
         <v/>
       </c>
       <c r="T161" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B161,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U161" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B161,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V161" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S161*10000+IFERROR(MATCH(J161,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W161" s="227" t="n"/>
       <c r="X161" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W161="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y161" s="227" t="n"/>
@@ -31836,28 +31820,28 @@
       <c r="P162" s="230" t="n"/>
       <c r="Q162" s="227" t="n"/>
       <c r="R162" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J162="已破獲未移送",J162="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S162" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D162="","",YEAR(D162)-1911),"")</f>
         <v/>
       </c>
       <c r="T162" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B162,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U162" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B162,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V162" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S162*10000+IFERROR(MATCH(J162,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W162" s="227" t="n"/>
       <c r="X162" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W162="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y162" s="227" t="n"/>
@@ -31881,28 +31865,28 @@
       <c r="P163" s="230" t="n"/>
       <c r="Q163" s="227" t="n"/>
       <c r="R163" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J163="已破獲未移送",J163="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S163" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D163="","",YEAR(D163)-1911),"")</f>
         <v/>
       </c>
       <c r="T163" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B163,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U163" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B163,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V163" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S163*10000+IFERROR(MATCH(J163,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W163" s="227" t="n"/>
       <c r="X163" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W163="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y163" s="227" t="n"/>
@@ -31926,28 +31910,28 @@
       <c r="P164" s="230" t="n"/>
       <c r="Q164" s="227" t="n"/>
       <c r="R164" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J164="已破獲未移送",J164="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S164" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D164="","",YEAR(D164)-1911),"")</f>
         <v/>
       </c>
       <c r="T164" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B164,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U164" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B164,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V164" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S164*10000+IFERROR(MATCH(J164,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W164" s="227" t="n"/>
       <c r="X164" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W164="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y164" s="227" t="n"/>
@@ -31971,28 +31955,28 @@
       <c r="P165" s="230" t="n"/>
       <c r="Q165" s="227" t="n"/>
       <c r="R165" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J165="已破獲未移送",J165="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S165" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D165="","",YEAR(D165)-1911),"")</f>
         <v/>
       </c>
       <c r="T165" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B165,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U165" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B165,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V165" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S165*10000+IFERROR(MATCH(J165,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W165" s="227" t="n"/>
       <c r="X165" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W165="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y165" s="227" t="n"/>
@@ -32016,28 +32000,28 @@
       <c r="P166" s="230" t="n"/>
       <c r="Q166" s="227" t="n"/>
       <c r="R166" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J166="已破獲未移送",J166="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S166" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D166="","",YEAR(D166)-1911),"")</f>
         <v/>
       </c>
       <c r="T166" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B166,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U166" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B166,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V166" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S166*10000+IFERROR(MATCH(J166,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W166" s="227" t="n"/>
       <c r="X166" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W166="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y166" s="227" t="n"/>
@@ -32061,28 +32045,28 @@
       <c r="P167" s="230" t="n"/>
       <c r="Q167" s="227" t="n"/>
       <c r="R167" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J167="已破獲未移送",J167="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S167" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D167="","",YEAR(D167)-1911),"")</f>
         <v/>
       </c>
       <c r="T167" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B167,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U167" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B167,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V167" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S167*10000+IFERROR(MATCH(J167,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W167" s="227" t="n"/>
       <c r="X167" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W167="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y167" s="227" t="n"/>
@@ -32106,28 +32090,28 @@
       <c r="P168" s="230" t="n"/>
       <c r="Q168" s="227" t="n"/>
       <c r="R168" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J168="已破獲未移送",J168="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S168" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D168="","",YEAR(D168)-1911),"")</f>
         <v/>
       </c>
       <c r="T168" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B168,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U168" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B168,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V168" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S168*10000+IFERROR(MATCH(J168,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W168" s="227" t="n"/>
       <c r="X168" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W168="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y168" s="227" t="n"/>
@@ -32151,28 +32135,28 @@
       <c r="P169" s="230" t="n"/>
       <c r="Q169" s="227" t="n"/>
       <c r="R169" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J169="已破獲未移送",J169="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S169" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D169="","",YEAR(D169)-1911),"")</f>
         <v/>
       </c>
       <c r="T169" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B169,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U169" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B169,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V169" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S169*10000+IFERROR(MATCH(J169,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W169" s="227" t="n"/>
       <c r="X169" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W169="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y169" s="227" t="n"/>
@@ -32196,28 +32180,28 @@
       <c r="P170" s="230" t="n"/>
       <c r="Q170" s="227" t="n"/>
       <c r="R170" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J170="已破獲未移送",J170="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S170" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D170="","",YEAR(D170)-1911),"")</f>
         <v/>
       </c>
       <c r="T170" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B170,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U170" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B170,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V170" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S170*10000+IFERROR(MATCH(J170,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W170" s="227" t="n"/>
       <c r="X170" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W170="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y170" s="227" t="n"/>
@@ -32241,28 +32225,28 @@
       <c r="P171" s="230" t="n"/>
       <c r="Q171" s="227" t="n"/>
       <c r="R171" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J171="已破獲未移送",J171="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S171" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D171="","",YEAR(D171)-1911),"")</f>
         <v/>
       </c>
       <c r="T171" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B171,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U171" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B171,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V171" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S171*10000+IFERROR(MATCH(J171,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W171" s="227" t="n"/>
       <c r="X171" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W171="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y171" s="227" t="n"/>
@@ -32286,28 +32270,28 @@
       <c r="P172" s="230" t="n"/>
       <c r="Q172" s="227" t="n"/>
       <c r="R172" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J172="已破獲未移送",J172="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S172" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D172="","",YEAR(D172)-1911),"")</f>
         <v/>
       </c>
       <c r="T172" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B172,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U172" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B172,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V172" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S172*10000+IFERROR(MATCH(J172,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W172" s="227" t="n"/>
       <c r="X172" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W172="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y172" s="227" t="n"/>
@@ -32331,28 +32315,28 @@
       <c r="P173" s="230" t="n"/>
       <c r="Q173" s="227" t="n"/>
       <c r="R173" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J173="已破獲未移送",J173="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S173" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D173="","",YEAR(D173)-1911),"")</f>
         <v/>
       </c>
       <c r="T173" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B173,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U173" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B173,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V173" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S173*10000+IFERROR(MATCH(J173,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W173" s="227" t="n"/>
       <c r="X173" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W173="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y173" s="227" t="n"/>
@@ -32376,28 +32360,28 @@
       <c r="P174" s="230" t="n"/>
       <c r="Q174" s="227" t="n"/>
       <c r="R174" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J174="已破獲未移送",J174="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S174" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D174="","",YEAR(D174)-1911),"")</f>
         <v/>
       </c>
       <c r="T174" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B174,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U174" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B174,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V174" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S174*10000+IFERROR(MATCH(J174,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W174" s="227" t="n"/>
       <c r="X174" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W174="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y174" s="227" t="n"/>
@@ -32421,28 +32405,28 @@
       <c r="P175" s="230" t="n"/>
       <c r="Q175" s="227" t="n"/>
       <c r="R175" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J175="已破獲未移送",J175="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S175" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D175="","",YEAR(D175)-1911),"")</f>
         <v/>
       </c>
       <c r="T175" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B175,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U175" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B175,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V175" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S175*10000+IFERROR(MATCH(J175,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W175" s="227" t="n"/>
       <c r="X175" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W175="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y175" s="227" t="n"/>
@@ -32466,28 +32450,28 @@
       <c r="P176" s="230" t="n"/>
       <c r="Q176" s="227" t="n"/>
       <c r="R176" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J176="已破獲未移送",J176="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S176" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D176="","",YEAR(D176)-1911),"")</f>
         <v/>
       </c>
       <c r="T176" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B176,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U176" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B176,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V176" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S176*10000+IFERROR(MATCH(J176,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W176" s="227" t="n"/>
       <c r="X176" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W176="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y176" s="227" t="n"/>
@@ -32511,28 +32495,28 @@
       <c r="P177" s="230" t="n"/>
       <c r="Q177" s="227" t="n"/>
       <c r="R177" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J177="已破獲未移送",J177="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S177" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D177="","",YEAR(D177)-1911),"")</f>
         <v/>
       </c>
       <c r="T177" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B177,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U177" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B177,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V177" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S177*10000+IFERROR(MATCH(J177,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W177" s="227" t="n"/>
       <c r="X177" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W177="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y177" s="227" t="n"/>
@@ -32556,28 +32540,28 @@
       <c r="P178" s="230" t="n"/>
       <c r="Q178" s="227" t="n"/>
       <c r="R178" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J178="已破獲未移送",J178="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S178" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D178="","",YEAR(D178)-1911),"")</f>
         <v/>
       </c>
       <c r="T178" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B178,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U178" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B178,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V178" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S178*10000+IFERROR(MATCH(J178,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W178" s="227" t="n"/>
       <c r="X178" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W178="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y178" s="227" t="n"/>
@@ -32601,28 +32585,28 @@
       <c r="P179" s="230" t="n"/>
       <c r="Q179" s="227" t="n"/>
       <c r="R179" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J179="已破獲未移送",J179="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S179" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D179="","",YEAR(D179)-1911),"")</f>
         <v/>
       </c>
       <c r="T179" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B179,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U179" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B179,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V179" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S179*10000+IFERROR(MATCH(J179,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W179" s="227" t="n"/>
       <c r="X179" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W179="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y179" s="227" t="n"/>
@@ -32646,28 +32630,28 @@
       <c r="P180" s="230" t="n"/>
       <c r="Q180" s="227" t="n"/>
       <c r="R180" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J180="已破獲未移送",J180="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S180" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D180="","",YEAR(D180)-1911),"")</f>
         <v/>
       </c>
       <c r="T180" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B180,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U180" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B180,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V180" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S180*10000+IFERROR(MATCH(J180,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W180" s="227" t="n"/>
       <c r="X180" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W180="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y180" s="227" t="n"/>
@@ -32691,28 +32675,28 @@
       <c r="P181" s="230" t="n"/>
       <c r="Q181" s="227" t="n"/>
       <c r="R181" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J181="已破獲未移送",J181="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S181" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D181="","",YEAR(D181)-1911),"")</f>
         <v/>
       </c>
       <c r="T181" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B181,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U181" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B181,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V181" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S181*10000+IFERROR(MATCH(J181,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W181" s="227" t="n"/>
       <c r="X181" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W181="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y181" s="227" t="n"/>
@@ -32736,28 +32720,28 @@
       <c r="P182" s="230" t="n"/>
       <c r="Q182" s="227" t="n"/>
       <c r="R182" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J182="已破獲未移送",J182="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S182" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D182="","",YEAR(D182)-1911),"")</f>
         <v/>
       </c>
       <c r="T182" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B182,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U182" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B182,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V182" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S182*10000+IFERROR(MATCH(J182,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W182" s="227" t="n"/>
       <c r="X182" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W182="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y182" s="227" t="n"/>
@@ -32781,28 +32765,28 @@
       <c r="P183" s="230" t="n"/>
       <c r="Q183" s="227" t="n"/>
       <c r="R183" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J183="已破獲未移送",J183="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S183" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D183="","",YEAR(D183)-1911),"")</f>
         <v/>
       </c>
       <c r="T183" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B183,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U183" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B183,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V183" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S183*10000+IFERROR(MATCH(J183,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W183" s="227" t="n"/>
       <c r="X183" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W183="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y183" s="227" t="n"/>
@@ -32826,28 +32810,28 @@
       <c r="P184" s="230" t="n"/>
       <c r="Q184" s="227" t="n"/>
       <c r="R184" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J184="已破獲未移送",J184="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S184" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D184="","",YEAR(D184)-1911),"")</f>
         <v/>
       </c>
       <c r="T184" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B184,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U184" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B184,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V184" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S184*10000+IFERROR(MATCH(J184,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W184" s="227" t="n"/>
       <c r="X184" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W184="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y184" s="227" t="n"/>
@@ -32871,28 +32855,28 @@
       <c r="P185" s="230" t="n"/>
       <c r="Q185" s="227" t="n"/>
       <c r="R185" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J185="已破獲未移送",J185="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S185" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D185="","",YEAR(D185)-1911),"")</f>
         <v/>
       </c>
       <c r="T185" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B185,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U185" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B185,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V185" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S185*10000+IFERROR(MATCH(J185,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W185" s="227" t="n"/>
       <c r="X185" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W185="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y185" s="227" t="n"/>
@@ -32916,28 +32900,28 @@
       <c r="P186" s="230" t="n"/>
       <c r="Q186" s="227" t="n"/>
       <c r="R186" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J186="已破獲未移送",J186="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S186" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D186="","",YEAR(D186)-1911),"")</f>
         <v/>
       </c>
       <c r="T186" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B186,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U186" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B186,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V186" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S186*10000+IFERROR(MATCH(J186,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W186" s="227" t="n"/>
       <c r="X186" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W186="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y186" s="227" t="n"/>
@@ -32961,28 +32945,28 @@
       <c r="P187" s="230" t="n"/>
       <c r="Q187" s="227" t="n"/>
       <c r="R187" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J187="已破獲未移送",J187="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S187" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D187="","",YEAR(D187)-1911),"")</f>
         <v/>
       </c>
       <c r="T187" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B187,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U187" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B187,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V187" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S187*10000+IFERROR(MATCH(J187,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W187" s="227" t="n"/>
       <c r="X187" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W187="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y187" s="227" t="n"/>
@@ -33006,28 +32990,28 @@
       <c r="P188" s="230" t="n"/>
       <c r="Q188" s="227" t="n"/>
       <c r="R188" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J188="已破獲未移送",J188="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S188" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D188="","",YEAR(D188)-1911),"")</f>
         <v/>
       </c>
       <c r="T188" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B188,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U188" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B188,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V188" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S188*10000+IFERROR(MATCH(J188,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W188" s="227" t="n"/>
       <c r="X188" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W188="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y188" s="227" t="n"/>
@@ -33051,28 +33035,28 @@
       <c r="P189" s="230" t="n"/>
       <c r="Q189" s="227" t="n"/>
       <c r="R189" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J189="已破獲未移送",J189="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S189" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D189="","",YEAR(D189)-1911),"")</f>
         <v/>
       </c>
       <c r="T189" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B189,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U189" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B189,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V189" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S189*10000+IFERROR(MATCH(J189,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W189" s="227" t="n"/>
       <c r="X189" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W189="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y189" s="227" t="n"/>
@@ -33096,28 +33080,28 @@
       <c r="P190" s="230" t="n"/>
       <c r="Q190" s="227" t="n"/>
       <c r="R190" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J190="已破獲未移送",J190="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S190" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D190="","",YEAR(D190)-1911),"")</f>
         <v/>
       </c>
       <c r="T190" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B190,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U190" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B190,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V190" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S190*10000+IFERROR(MATCH(J190,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W190" s="227" t="n"/>
       <c r="X190" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W190="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y190" s="227" t="n"/>
@@ -33141,28 +33125,28 @@
       <c r="P191" s="230" t="n"/>
       <c r="Q191" s="227" t="n"/>
       <c r="R191" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J191="已破獲未移送",J191="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S191" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D191="","",YEAR(D191)-1911),"")</f>
         <v/>
       </c>
       <c r="T191" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B191,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U191" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B191,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V191" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S191*10000+IFERROR(MATCH(J191,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W191" s="227" t="n"/>
       <c r="X191" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W191="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y191" s="227" t="n"/>
@@ -33186,28 +33170,28 @@
       <c r="P192" s="230" t="n"/>
       <c r="Q192" s="227" t="n"/>
       <c r="R192" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J192="已破獲未移送",J192="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S192" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D192="","",YEAR(D192)-1911),"")</f>
         <v/>
       </c>
       <c r="T192" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B192,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U192" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B192,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V192" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S192*10000+IFERROR(MATCH(J192,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W192" s="227" t="n"/>
       <c r="X192" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W192="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y192" s="227" t="n"/>
@@ -33231,28 +33215,28 @@
       <c r="P193" s="230" t="n"/>
       <c r="Q193" s="227" t="n"/>
       <c r="R193" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J193="已破獲未移送",J193="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S193" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D193="","",YEAR(D193)-1911),"")</f>
         <v/>
       </c>
       <c r="T193" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B193,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U193" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B193,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V193" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S193*10000+IFERROR(MATCH(J193,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W193" s="227" t="n"/>
       <c r="X193" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W193="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y193" s="227" t="n"/>
@@ -33276,28 +33260,28 @@
       <c r="P194" s="230" t="n"/>
       <c r="Q194" s="227" t="n"/>
       <c r="R194" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J194="已破獲未移送",J194="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S194" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D194="","",YEAR(D194)-1911),"")</f>
         <v/>
       </c>
       <c r="T194" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B194,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U194" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B194,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V194" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S194*10000+IFERROR(MATCH(J194,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W194" s="227" t="n"/>
       <c r="X194" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W194="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y194" s="227" t="n"/>
@@ -33321,28 +33305,28 @@
       <c r="P195" s="230" t="n"/>
       <c r="Q195" s="227" t="n"/>
       <c r="R195" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J195="已破獲未移送",J195="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S195" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D195="","",YEAR(D195)-1911),"")</f>
         <v/>
       </c>
       <c r="T195" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B195,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U195" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B195,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V195" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S195*10000+IFERROR(MATCH(J195,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W195" s="227" t="n"/>
       <c r="X195" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W195="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y195" s="227" t="n"/>
@@ -33366,28 +33350,28 @@
       <c r="P196" s="230" t="n"/>
       <c r="Q196" s="227" t="n"/>
       <c r="R196" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J196="已破獲未移送",J196="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S196" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D196="","",YEAR(D196)-1911),"")</f>
         <v/>
       </c>
       <c r="T196" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B196,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U196" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B196,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V196" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S196*10000+IFERROR(MATCH(J196,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W196" s="227" t="n"/>
       <c r="X196" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W196="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y196" s="227" t="n"/>
@@ -33411,28 +33395,28 @@
       <c r="P197" s="230" t="n"/>
       <c r="Q197" s="227" t="n"/>
       <c r="R197" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J197="已破獲未移送",J197="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S197" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D197="","",YEAR(D197)-1911),"")</f>
         <v/>
       </c>
       <c r="T197" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B197,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U197" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B197,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V197" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S197*10000+IFERROR(MATCH(J197,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W197" s="227" t="n"/>
       <c r="X197" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W197="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y197" s="227" t="n"/>
@@ -33456,28 +33440,28 @@
       <c r="P198" s="230" t="n"/>
       <c r="Q198" s="227" t="n"/>
       <c r="R198" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J198="已破獲未移送",J198="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S198" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D198="","",YEAR(D198)-1911),"")</f>
         <v/>
       </c>
       <c r="T198" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B198,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U198" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B198,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V198" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S198*10000+IFERROR(MATCH(J198,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W198" s="227" t="n"/>
       <c r="X198" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W198="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y198" s="227" t="n"/>
@@ -33501,28 +33485,28 @@
       <c r="P199" s="230" t="n"/>
       <c r="Q199" s="227" t="n"/>
       <c r="R199" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J199="已破獲未移送",J199="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S199" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D199="","",YEAR(D199)-1911),"")</f>
         <v/>
       </c>
       <c r="T199" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B199,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U199" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B199,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V199" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S199*10000+IFERROR(MATCH(J199,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W199" s="227" t="n"/>
       <c r="X199" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W199="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y199" s="227" t="n"/>
@@ -33546,28 +33530,28 @@
       <c r="P200" s="230" t="n"/>
       <c r="Q200" s="227" t="n"/>
       <c r="R200" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J200="已破獲未移送",J200="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S200" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D200="","",YEAR(D200)-1911),"")</f>
         <v/>
       </c>
       <c r="T200" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B200,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U200" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B200,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V200" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S200*10000+IFERROR(MATCH(J200,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W200" s="227" t="n"/>
       <c r="X200" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W200="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y200" s="227" t="n"/>
@@ -33591,28 +33575,28 @@
       <c r="P201" s="230" t="n"/>
       <c r="Q201" s="227" t="n"/>
       <c r="R201" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J201="已破獲未移送",J201="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S201" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D201="","",YEAR(D201)-1911),"")</f>
         <v/>
       </c>
       <c r="T201" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B201,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U201" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B201,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V201" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S201*10000+IFERROR(MATCH(J201,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W201" s="227" t="n"/>
       <c r="X201" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W201="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y201" s="227" t="n"/>
@@ -33636,28 +33620,28 @@
       <c r="P202" s="230" t="n"/>
       <c r="Q202" s="227" t="n"/>
       <c r="R202" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J202="已破獲未移送",J202="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S202" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D202="","",YEAR(D202)-1911),"")</f>
         <v/>
       </c>
       <c r="T202" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B202,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U202" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B202,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V202" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S202*10000+IFERROR(MATCH(J202,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W202" s="227" t="n"/>
       <c r="X202" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W202="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y202" s="227" t="n"/>
@@ -33681,28 +33665,28 @@
       <c r="P203" s="230" t="n"/>
       <c r="Q203" s="227" t="n"/>
       <c r="R203" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J203="已破獲未移送",J203="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S203" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D203="","",YEAR(D203)-1911),"")</f>
         <v/>
       </c>
       <c r="T203" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B203,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U203" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B203,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V203" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S203*10000+IFERROR(MATCH(J203,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W203" s="227" t="n"/>
       <c r="X203" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W203="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y203" s="227" t="n"/>
@@ -33726,28 +33710,28 @@
       <c r="P204" s="230" t="n"/>
       <c r="Q204" s="227" t="n"/>
       <c r="R204" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J204="已破獲未移送",J204="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S204" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D204="","",YEAR(D204)-1911),"")</f>
         <v/>
       </c>
       <c r="T204" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B204,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U204" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B204,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V204" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S204*10000+IFERROR(MATCH(J204,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W204" s="227" t="n"/>
       <c r="X204" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W204="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y204" s="227" t="n"/>
@@ -33771,28 +33755,28 @@
       <c r="P205" s="230" t="n"/>
       <c r="Q205" s="227" t="n"/>
       <c r="R205" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J205="已破獲未移送",J205="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S205" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D205="","",YEAR(D205)-1911),"")</f>
         <v/>
       </c>
       <c r="T205" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B205,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U205" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B205,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V205" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S205*10000+IFERROR(MATCH(J205,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W205" s="227" t="n"/>
       <c r="X205" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W205="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y205" s="227" t="n"/>
@@ -33816,28 +33800,28 @@
       <c r="P206" s="230" t="n"/>
       <c r="Q206" s="227" t="n"/>
       <c r="R206" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J206="已破獲未移送",J206="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S206" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D206="","",YEAR(D206)-1911),"")</f>
         <v/>
       </c>
       <c r="T206" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B206,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U206" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B206,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V206" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S206*10000+IFERROR(MATCH(J206,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W206" s="227" t="n"/>
       <c r="X206" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W206="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y206" s="227" t="n"/>
@@ -33861,28 +33845,28 @@
       <c r="P207" s="230" t="n"/>
       <c r="Q207" s="227" t="n"/>
       <c r="R207" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J207="已破獲未移送",J207="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S207" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D207="","",YEAR(D207)-1911),"")</f>
         <v/>
       </c>
       <c r="T207" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B207,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U207" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B207,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V207" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S207*10000+IFERROR(MATCH(J207,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W207" s="227" t="n"/>
       <c r="X207" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W207="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y207" s="227" t="n"/>
@@ -33906,28 +33890,28 @@
       <c r="P208" s="230" t="n"/>
       <c r="Q208" s="227" t="n"/>
       <c r="R208" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J208="已破獲未移送",J208="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S208" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D208="","",YEAR(D208)-1911),"")</f>
         <v/>
       </c>
       <c r="T208" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B208,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U208" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B208,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V208" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S208*10000+IFERROR(MATCH(J208,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W208" s="227" t="n"/>
       <c r="X208" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W208="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y208" s="227" t="n"/>
@@ -33951,28 +33935,28 @@
       <c r="P209" s="230" t="n"/>
       <c r="Q209" s="227" t="n"/>
       <c r="R209" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J209="已破獲未移送",J209="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S209" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D209="","",YEAR(D209)-1911),"")</f>
         <v/>
       </c>
       <c r="T209" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B209,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U209" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B209,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V209" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S209*10000+IFERROR(MATCH(J209,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W209" s="227" t="n"/>
       <c r="X209" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W209="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y209" s="227" t="n"/>
@@ -33996,28 +33980,28 @@
       <c r="P210" s="230" t="n"/>
       <c r="Q210" s="227" t="n"/>
       <c r="R210" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J210="已破獲未移送",J210="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S210" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D210="","",YEAR(D210)-1911),"")</f>
         <v/>
       </c>
       <c r="T210" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B210,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U210" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B210,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V210" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S210*10000+IFERROR(MATCH(J210,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W210" s="227" t="n"/>
       <c r="X210" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W210="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y210" s="227" t="n"/>
@@ -34041,28 +34025,28 @@
       <c r="P211" s="230" t="n"/>
       <c r="Q211" s="227" t="n"/>
       <c r="R211" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J211="已破獲未移送",J211="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S211" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D211="","",YEAR(D211)-1911),"")</f>
         <v/>
       </c>
       <c r="T211" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B211,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U211" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B211,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V211" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S211*10000+IFERROR(MATCH(J211,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W211" s="227" t="n"/>
       <c r="X211" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W211="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y211" s="227" t="n"/>
@@ -34086,28 +34070,28 @@
       <c r="P212" s="230" t="n"/>
       <c r="Q212" s="227" t="n"/>
       <c r="R212" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J212="已破獲未移送",J212="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S212" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D212="","",YEAR(D212)-1911),"")</f>
         <v/>
       </c>
       <c r="T212" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B212,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U212" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B212,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V212" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S212*10000+IFERROR(MATCH(J212,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W212" s="227" t="n"/>
       <c r="X212" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W212="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y212" s="227" t="n"/>
@@ -34131,28 +34115,28 @@
       <c r="P213" s="230" t="n"/>
       <c r="Q213" s="227" t="n"/>
       <c r="R213" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J213="已破獲未移送",J213="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S213" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D213="","",YEAR(D213)-1911),"")</f>
         <v/>
       </c>
       <c r="T213" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B213,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U213" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B213,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V213" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S213*10000+IFERROR(MATCH(J213,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W213" s="227" t="n"/>
       <c r="X213" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W213="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y213" s="227" t="n"/>
@@ -34176,28 +34160,28 @@
       <c r="P214" s="230" t="n"/>
       <c r="Q214" s="227" t="n"/>
       <c r="R214" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J214="已破獲未移送",J214="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S214" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D214="","",YEAR(D214)-1911),"")</f>
         <v/>
       </c>
       <c r="T214" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B214,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U214" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B214,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V214" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S214*10000+IFERROR(MATCH(J214,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W214" s="227" t="n"/>
       <c r="X214" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W214="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y214" s="227" t="n"/>
@@ -34221,28 +34205,28 @@
       <c r="P215" s="230" t="n"/>
       <c r="Q215" s="227" t="n"/>
       <c r="R215" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J215="已破獲未移送",J215="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S215" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D215="","",YEAR(D215)-1911),"")</f>
         <v/>
       </c>
       <c r="T215" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B215,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U215" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B215,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V215" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S215*10000+IFERROR(MATCH(J215,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W215" s="227" t="n"/>
       <c r="X215" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W215="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y215" s="227" t="n"/>
@@ -34266,28 +34250,28 @@
       <c r="P216" s="230" t="n"/>
       <c r="Q216" s="227" t="n"/>
       <c r="R216" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J216="已破獲未移送",J216="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S216" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D216="","",YEAR(D216)-1911),"")</f>
         <v/>
       </c>
       <c r="T216" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B216,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U216" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B216,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V216" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S216*10000+IFERROR(MATCH(J216,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W216" s="227" t="n"/>
       <c r="X216" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W216="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y216" s="227" t="n"/>
@@ -34311,28 +34295,28 @@
       <c r="P217" s="230" t="n"/>
       <c r="Q217" s="227" t="n"/>
       <c r="R217" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J217="已破獲未移送",J217="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S217" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D217="","",YEAR(D217)-1911),"")</f>
         <v/>
       </c>
       <c r="T217" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B217,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U217" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B217,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V217" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S217*10000+IFERROR(MATCH(J217,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W217" s="227" t="n"/>
       <c r="X217" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W217="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y217" s="227" t="n"/>
@@ -34356,28 +34340,28 @@
       <c r="P218" s="230" t="n"/>
       <c r="Q218" s="227" t="n"/>
       <c r="R218" s="15">
-        <f>IFERROR(IF(OR([@案件狀況]="已破獲未移送",[@案件狀況]="已移送"),"是","否"),"")</f>
+        <f>IFERROR(IF(OR(J218="已破獲未移送",J218="已移送"),"是","否"),"")</f>
         <v/>
       </c>
       <c r="S218" s="15">
-        <f>IFERROR(IF([@發生時間]="","",YEAR([@發生時間])-1911),"")</f>
+        <f>IFERROR(IF(D218="","",YEAR(D218)-1911),"")</f>
         <v/>
       </c>
       <c r="T218" s="15">
-        <f>IFERROR(INDEX(案類分類清單,MATCH([@案類],案類名稱清單,0)),"")</f>
+        <f>IFERROR(INDEX(案類分類清單,MATCH(B218,案類名稱清單,0)),"")</f>
         <v/>
       </c>
       <c r="U218" s="15">
-        <f>IFERROR(INDEX(納入全般清單,MATCH([@案類],案類名稱清單,0)),"否")</f>
+        <f>IFERROR(INDEX(納入全般清單,MATCH(B218,案類名稱清單,0)),"否")</f>
         <v/>
       </c>
       <c r="V218" s="15">
-        <f>IFERROR([@歸屬年度]*10000+IFERROR(MATCH([@案件狀況],{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
+        <f>IFERROR(S218*10000+IFERROR(MATCH(J218,{"尚未偵破","已破獲未移送","已移送","簽結"},0),0)*100+ROW(),0)</f>
         <v/>
       </c>
       <c r="W218" s="227" t="n"/>
       <c r="X218" s="15">
-        <f>IFERROR(IF([@績效類別]="","是","否"),"是")</f>
+        <f>IFERROR(IF(W218="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="Y218" s="227" t="n"/>
@@ -40907,19 +40891,19 @@
       <c r="I15" s="14" t="inlineStr"/>
       <c r="J15" s="45" t="n"/>
       <c r="K15" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J15="","",今日-J15),"")</f>
         <v/>
       </c>
       <c r="L15" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H15="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H15)))&gt;0,AND(ISNUMBER(K15),K15&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M15" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H15="","○ 未填",IF(ISNUMBER(SEARCH("解除",H15)),"○ 結束",IF(AND(ISNUMBER(K15),K15&gt;30),"● 紅",IF(L15=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N15" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H15)),AND(ISNUMBER(K15),K15&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P15" s="15">
@@ -40951,19 +40935,19 @@
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="45" t="n"/>
       <c r="K16" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J16="","",今日-J16),"")</f>
         <v/>
       </c>
       <c r="L16" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H16="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H16)))&gt;0,AND(ISNUMBER(K16),K16&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M16" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H16="","○ 未填",IF(ISNUMBER(SEARCH("解除",H16)),"○ 結束",IF(AND(ISNUMBER(K16),K16&gt;30),"● 紅",IF(L16=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N16" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H16)),AND(ISNUMBER(K16),K16&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P16" s="15">
@@ -40995,19 +40979,19 @@
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J17="","",今日-J17),"")</f>
         <v/>
       </c>
       <c r="L17" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H17="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H17)))&gt;0,AND(ISNUMBER(K17),K17&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M17" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H17="","○ 未填",IF(ISNUMBER(SEARCH("解除",H17)),"○ 結束",IF(AND(ISNUMBER(K17),K17&gt;30),"● 紅",IF(L17=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N17" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H17)),AND(ISNUMBER(K17),K17&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P17" s="15">
@@ -41039,19 +41023,19 @@
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="45" t="n"/>
       <c r="K18" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J18="","",今日-J18),"")</f>
         <v/>
       </c>
       <c r="L18" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H18="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H18)))&gt;0,AND(ISNUMBER(K18),K18&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M18" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H18="","○ 未填",IF(ISNUMBER(SEARCH("解除",H18)),"○ 結束",IF(AND(ISNUMBER(K18),K18&gt;30),"● 紅",IF(L18=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N18" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H18)),AND(ISNUMBER(K18),K18&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P18" s="15">
@@ -41083,19 +41067,19 @@
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="45" t="n"/>
       <c r="K19" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J19="","",今日-J19),"")</f>
         <v/>
       </c>
       <c r="L19" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H19="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H19)))&gt;0,AND(ISNUMBER(K19),K19&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M19" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H19="","○ 未填",IF(ISNUMBER(SEARCH("解除",H19)),"○ 結束",IF(AND(ISNUMBER(K19),K19&gt;30),"● 紅",IF(L19=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N19" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H19)),AND(ISNUMBER(K19),K19&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P19" s="15">
@@ -41127,19 +41111,19 @@
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="45" t="n"/>
       <c r="K20" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J20="","",今日-J20),"")</f>
         <v/>
       </c>
       <c r="L20" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H20="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H20)))&gt;0,AND(ISNUMBER(K20),K20&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M20" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H20="","○ 未填",IF(ISNUMBER(SEARCH("解除",H20)),"○ 結束",IF(AND(ISNUMBER(K20),K20&gt;30),"● 紅",IF(L20=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N20" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H20)),AND(ISNUMBER(K20),K20&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P20" s="15">
@@ -41171,19 +41155,19 @@
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="45" t="n"/>
       <c r="K21" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J21="","",今日-J21),"")</f>
         <v/>
       </c>
       <c r="L21" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H21="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H21)))&gt;0,AND(ISNUMBER(K21),K21&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M21" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H21="","○ 未填",IF(ISNUMBER(SEARCH("解除",H21)),"○ 結束",IF(AND(ISNUMBER(K21),K21&gt;30),"● 紅",IF(L21=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N21" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H21)),AND(ISNUMBER(K21),K21&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P21" s="15">
@@ -41215,19 +41199,19 @@
       <c r="I22" s="14" t="n"/>
       <c r="J22" s="45" t="n"/>
       <c r="K22" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J22="","",今日-J22),"")</f>
         <v/>
       </c>
       <c r="L22" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H22="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H22)))&gt;0,AND(ISNUMBER(K22),K22&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M22" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H22="","○ 未填",IF(ISNUMBER(SEARCH("解除",H22)),"○ 結束",IF(AND(ISNUMBER(K22),K22&gt;30),"● 紅",IF(L22=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N22" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H22)),AND(ISNUMBER(K22),K22&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P22" s="15">
@@ -41259,19 +41243,19 @@
       <c r="I23" s="14" t="n"/>
       <c r="J23" s="45" t="n"/>
       <c r="K23" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J23="","",今日-J23),"")</f>
         <v/>
       </c>
       <c r="L23" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H23="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H23)))&gt;0,AND(ISNUMBER(K23),K23&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M23" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H23="","○ 未填",IF(ISNUMBER(SEARCH("解除",H23)),"○ 結束",IF(AND(ISNUMBER(K23),K23&gt;30),"● 紅",IF(L23=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N23" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H23)),AND(ISNUMBER(K23),K23&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P23" s="15">
@@ -41303,19 +41287,19 @@
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="45" t="n"/>
       <c r="K24" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J24="","",今日-J24),"")</f>
         <v/>
       </c>
       <c r="L24" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H24="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H24)))&gt;0,AND(ISNUMBER(K24),K24&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M24" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H24="","○ 未填",IF(ISNUMBER(SEARCH("解除",H24)),"○ 結束",IF(AND(ISNUMBER(K24),K24&gt;30),"● 紅",IF(L24=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N24" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H24)),AND(ISNUMBER(K24),K24&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P24" s="15">
@@ -41347,19 +41331,19 @@
       <c r="I25" s="14" t="n"/>
       <c r="J25" s="45" t="n"/>
       <c r="K25" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J25="","",今日-J25),"")</f>
         <v/>
       </c>
       <c r="L25" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H25="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H25)))&gt;0,AND(ISNUMBER(K25),K25&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M25" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H25="","○ 未填",IF(ISNUMBER(SEARCH("解除",H25)),"○ 結束",IF(AND(ISNUMBER(K25),K25&gt;30),"● 紅",IF(L25=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N25" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H25)),AND(ISNUMBER(K25),K25&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P25" s="15">
@@ -41391,19 +41375,19 @@
       <c r="I26" s="14" t="n"/>
       <c r="J26" s="45" t="n"/>
       <c r="K26" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J26="","",今日-J26),"")</f>
         <v/>
       </c>
       <c r="L26" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H26="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H26)))&gt;0,AND(ISNUMBER(K26),K26&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M26" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H26="","○ 未填",IF(ISNUMBER(SEARCH("解除",H26)),"○ 結束",IF(AND(ISNUMBER(K26),K26&gt;30),"● 紅",IF(L26=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N26" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H26)),AND(ISNUMBER(K26),K26&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P26" s="15">
@@ -41435,19 +41419,19 @@
       <c r="I27" s="14" t="n"/>
       <c r="J27" s="45" t="n"/>
       <c r="K27" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J27="","",今日-J27),"")</f>
         <v/>
       </c>
       <c r="L27" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H27="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H27)))&gt;0,AND(ISNUMBER(K27),K27&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M27" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H27="","○ 未填",IF(ISNUMBER(SEARCH("解除",H27)),"○ 結束",IF(AND(ISNUMBER(K27),K27&gt;30),"● 紅",IF(L27=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N27" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H27)),AND(ISNUMBER(K27),K27&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P27" s="15">
@@ -41479,19 +41463,19 @@
       <c r="I28" s="14" t="n"/>
       <c r="J28" s="45" t="n"/>
       <c r="K28" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J28="","",今日-J28),"")</f>
         <v/>
       </c>
       <c r="L28" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H28="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H28)))&gt;0,AND(ISNUMBER(K28),K28&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M28" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H28="","○ 未填",IF(ISNUMBER(SEARCH("解除",H28)),"○ 結束",IF(AND(ISNUMBER(K28),K28&gt;30),"● 紅",IF(L28=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N28" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H28)),AND(ISNUMBER(K28),K28&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P28" s="15">
@@ -41523,19 +41507,19 @@
       <c r="I29" s="14" t="n"/>
       <c r="J29" s="45" t="n"/>
       <c r="K29" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J29="","",今日-J29),"")</f>
         <v/>
       </c>
       <c r="L29" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H29="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H29)))&gt;0,AND(ISNUMBER(K29),K29&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M29" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H29="","○ 未填",IF(ISNUMBER(SEARCH("解除",H29)),"○ 結束",IF(AND(ISNUMBER(K29),K29&gt;30),"● 紅",IF(L29=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N29" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H29)),AND(ISNUMBER(K29),K29&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P29" s="15">
@@ -41567,19 +41551,19 @@
       <c r="I30" s="14" t="n"/>
       <c r="J30" s="45" t="n"/>
       <c r="K30" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J30="","",今日-J30),"")</f>
         <v/>
       </c>
       <c r="L30" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H30="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H30)))&gt;0,AND(ISNUMBER(K30),K30&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M30" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H30="","○ 未填",IF(ISNUMBER(SEARCH("解除",H30)),"○ 結束",IF(AND(ISNUMBER(K30),K30&gt;30),"● 紅",IF(L30=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N30" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H30)),AND(ISNUMBER(K30),K30&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P30" s="15">
@@ -41611,19 +41595,19 @@
       <c r="I31" s="14" t="n"/>
       <c r="J31" s="45" t="n"/>
       <c r="K31" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J31="","",今日-J31),"")</f>
         <v/>
       </c>
       <c r="L31" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H31="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H31)))&gt;0,AND(ISNUMBER(K31),K31&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M31" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H31="","○ 未填",IF(ISNUMBER(SEARCH("解除",H31)),"○ 結束",IF(AND(ISNUMBER(K31),K31&gt;30),"● 紅",IF(L31=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N31" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H31)),AND(ISNUMBER(K31),K31&gt;30)),1,0),0)</f>
         <v/>
       </c>
       <c r="P31" s="82">
@@ -41643,19 +41627,19 @@
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="45" t="n"/>
       <c r="K32" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J32="","",今日-J32),"")</f>
         <v/>
       </c>
       <c r="L32" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H32="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H32)))&gt;0,AND(ISNUMBER(K32),K32&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M32" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H32="","○ 未填",IF(ISNUMBER(SEARCH("解除",H32)),"○ 結束",IF(AND(ISNUMBER(K32),K32&gt;30),"● 紅",IF(L32=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N32" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H32)),AND(ISNUMBER(K32),K32&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41671,19 +41655,19 @@
       <c r="I33" s="14" t="n"/>
       <c r="J33" s="45" t="n"/>
       <c r="K33" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J33="","",今日-J33),"")</f>
         <v/>
       </c>
       <c r="L33" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H33="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H33)))&gt;0,AND(ISNUMBER(K33),K33&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M33" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H33="","○ 未填",IF(ISNUMBER(SEARCH("解除",H33)),"○ 結束",IF(AND(ISNUMBER(K33),K33&gt;30),"● 紅",IF(L33=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N33" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H33)),AND(ISNUMBER(K33),K33&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41699,19 +41683,19 @@
       <c r="I34" s="14" t="n"/>
       <c r="J34" s="45" t="n"/>
       <c r="K34" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J34="","",今日-J34),"")</f>
         <v/>
       </c>
       <c r="L34" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H34="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H34)))&gt;0,AND(ISNUMBER(K34),K34&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M34" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H34="","○ 未填",IF(ISNUMBER(SEARCH("解除",H34)),"○ 結束",IF(AND(ISNUMBER(K34),K34&gt;30),"● 紅",IF(L34=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N34" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H34)),AND(ISNUMBER(K34),K34&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41727,19 +41711,19 @@
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="45" t="n"/>
       <c r="K35" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J35="","",今日-J35),"")</f>
         <v/>
       </c>
       <c r="L35" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H35="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H35)))&gt;0,AND(ISNUMBER(K35),K35&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M35" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H35="","○ 未填",IF(ISNUMBER(SEARCH("解除",H35)),"○ 結束",IF(AND(ISNUMBER(K35),K35&gt;30),"● 紅",IF(L35=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N35" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H35)),AND(ISNUMBER(K35),K35&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41755,19 +41739,19 @@
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="45" t="n"/>
       <c r="K36" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J36="","",今日-J36),"")</f>
         <v/>
       </c>
       <c r="L36" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H36="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H36)))&gt;0,AND(ISNUMBER(K36),K36&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M36" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H36="","○ 未填",IF(ISNUMBER(SEARCH("解除",H36)),"○ 結束",IF(AND(ISNUMBER(K36),K36&gt;30),"● 紅",IF(L36=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N36" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H36)),AND(ISNUMBER(K36),K36&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41783,19 +41767,19 @@
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="45" t="n"/>
       <c r="K37" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J37="","",今日-J37),"")</f>
         <v/>
       </c>
       <c r="L37" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H37="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H37)))&gt;0,AND(ISNUMBER(K37),K37&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M37" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H37="","○ 未填",IF(ISNUMBER(SEARCH("解除",H37)),"○ 結束",IF(AND(ISNUMBER(K37),K37&gt;30),"● 紅",IF(L37=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N37" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H37)),AND(ISNUMBER(K37),K37&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41811,19 +41795,19 @@
       <c r="I38" s="14" t="n"/>
       <c r="J38" s="45" t="n"/>
       <c r="K38" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J38="","",今日-J38),"")</f>
         <v/>
       </c>
       <c r="L38" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H38="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H38)))&gt;0,AND(ISNUMBER(K38),K38&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M38" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H38="","○ 未填",IF(ISNUMBER(SEARCH("解除",H38)),"○ 結束",IF(AND(ISNUMBER(K38),K38&gt;30),"● 紅",IF(L38=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N38" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H38)),AND(ISNUMBER(K38),K38&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41839,19 +41823,19 @@
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="45" t="n"/>
       <c r="K39" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J39="","",今日-J39),"")</f>
         <v/>
       </c>
       <c r="L39" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H39="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H39)))&gt;0,AND(ISNUMBER(K39),K39&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M39" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H39="","○ 未填",IF(ISNUMBER(SEARCH("解除",H39)),"○ 結束",IF(AND(ISNUMBER(K39),K39&gt;30),"● 紅",IF(L39=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N39" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H39)),AND(ISNUMBER(K39),K39&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41867,19 +41851,19 @@
       <c r="I40" s="14" t="n"/>
       <c r="J40" s="45" t="n"/>
       <c r="K40" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J40="","",今日-J40),"")</f>
         <v/>
       </c>
       <c r="L40" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H40="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H40)))&gt;0,AND(ISNUMBER(K40),K40&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M40" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H40="","○ 未填",IF(ISNUMBER(SEARCH("解除",H40)),"○ 結束",IF(AND(ISNUMBER(K40),K40&gt;30),"● 紅",IF(L40=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N40" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H40)),AND(ISNUMBER(K40),K40&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41895,19 +41879,19 @@
       <c r="I41" s="14" t="n"/>
       <c r="J41" s="45" t="n"/>
       <c r="K41" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J41="","",今日-J41),"")</f>
         <v/>
       </c>
       <c r="L41" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H41="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H41)))&gt;0,AND(ISNUMBER(K41),K41&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M41" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H41="","○ 未填",IF(ISNUMBER(SEARCH("解除",H41)),"○ 結束",IF(AND(ISNUMBER(K41),K41&gt;30),"● 紅",IF(L41=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N41" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H41)),AND(ISNUMBER(K41),K41&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41923,19 +41907,19 @@
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="45" t="n"/>
       <c r="K42" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J42="","",今日-J42),"")</f>
         <v/>
       </c>
       <c r="L42" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H42="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H42)))&gt;0,AND(ISNUMBER(K42),K42&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M42" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H42="","○ 未填",IF(ISNUMBER(SEARCH("解除",H42)),"○ 結束",IF(AND(ISNUMBER(K42),K42&gt;30),"● 紅",IF(L42=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N42" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H42)),AND(ISNUMBER(K42),K42&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41951,19 +41935,19 @@
       <c r="I43" s="14" t="n"/>
       <c r="J43" s="45" t="n"/>
       <c r="K43" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J43="","",今日-J43),"")</f>
         <v/>
       </c>
       <c r="L43" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H43="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H43)))&gt;0,AND(ISNUMBER(K43),K43&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M43" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H43="","○ 未填",IF(ISNUMBER(SEARCH("解除",H43)),"○ 結束",IF(AND(ISNUMBER(K43),K43&gt;30),"● 紅",IF(L43=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N43" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H43)),AND(ISNUMBER(K43),K43&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -41979,19 +41963,19 @@
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="45" t="n"/>
       <c r="K44" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J44="","",今日-J44),"")</f>
         <v/>
       </c>
       <c r="L44" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H44="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H44)))&gt;0,AND(ISNUMBER(K44),K44&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M44" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H44="","○ 未填",IF(ISNUMBER(SEARCH("解除",H44)),"○ 結束",IF(AND(ISNUMBER(K44),K44&gt;30),"● 紅",IF(L44=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N44" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H44)),AND(ISNUMBER(K44),K44&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42007,19 +41991,19 @@
       <c r="I45" s="14" t="n"/>
       <c r="J45" s="45" t="n"/>
       <c r="K45" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J45="","",今日-J45),"")</f>
         <v/>
       </c>
       <c r="L45" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H45="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H45)))&gt;0,AND(ISNUMBER(K45),K45&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M45" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H45="","○ 未填",IF(ISNUMBER(SEARCH("解除",H45)),"○ 結束",IF(AND(ISNUMBER(K45),K45&gt;30),"● 紅",IF(L45=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N45" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H45)),AND(ISNUMBER(K45),K45&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42035,19 +42019,19 @@
       <c r="I46" s="14" t="n"/>
       <c r="J46" s="45" t="n"/>
       <c r="K46" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J46="","",今日-J46),"")</f>
         <v/>
       </c>
       <c r="L46" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H46="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H46)))&gt;0,AND(ISNUMBER(K46),K46&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M46" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H46="","○ 未填",IF(ISNUMBER(SEARCH("解除",H46)),"○ 結束",IF(AND(ISNUMBER(K46),K46&gt;30),"● 紅",IF(L46=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N46" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H46)),AND(ISNUMBER(K46),K46&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42063,19 +42047,19 @@
       <c r="I47" s="14" t="n"/>
       <c r="J47" s="45" t="n"/>
       <c r="K47" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J47="","",今日-J47),"")</f>
         <v/>
       </c>
       <c r="L47" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H47="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H47)))&gt;0,AND(ISNUMBER(K47),K47&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M47" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H47="","○ 未填",IF(ISNUMBER(SEARCH("解除",H47)),"○ 結束",IF(AND(ISNUMBER(K47),K47&gt;30),"● 紅",IF(L47=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N47" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H47)),AND(ISNUMBER(K47),K47&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42091,19 +42075,19 @@
       <c r="I48" s="14" t="n"/>
       <c r="J48" s="45" t="n"/>
       <c r="K48" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J48="","",今日-J48),"")</f>
         <v/>
       </c>
       <c r="L48" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H48="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H48)))&gt;0,AND(ISNUMBER(K48),K48&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M48" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H48="","○ 未填",IF(ISNUMBER(SEARCH("解除",H48)),"○ 結束",IF(AND(ISNUMBER(K48),K48&gt;30),"● 紅",IF(L48=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N48" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H48)),AND(ISNUMBER(K48),K48&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42119,19 +42103,19 @@
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="45" t="n"/>
       <c r="K49" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J49="","",今日-J49),"")</f>
         <v/>
       </c>
       <c r="L49" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H49="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H49)))&gt;0,AND(ISNUMBER(K49),K49&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M49" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H49="","○ 未填",IF(ISNUMBER(SEARCH("解除",H49)),"○ 結束",IF(AND(ISNUMBER(K49),K49&gt;30),"● 紅",IF(L49=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N49" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H49)),AND(ISNUMBER(K49),K49&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42147,19 +42131,19 @@
       <c r="I50" s="14" t="n"/>
       <c r="J50" s="45" t="n"/>
       <c r="K50" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J50="","",今日-J50),"")</f>
         <v/>
       </c>
       <c r="L50" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H50="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H50)))&gt;0,AND(ISNUMBER(K50),K50&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M50" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H50="","○ 未填",IF(ISNUMBER(SEARCH("解除",H50)),"○ 結束",IF(AND(ISNUMBER(K50),K50&gt;30),"● 紅",IF(L50=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N50" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H50)),AND(ISNUMBER(K50),K50&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42175,19 +42159,19 @@
       <c r="I51" s="14" t="n"/>
       <c r="J51" s="45" t="n"/>
       <c r="K51" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J51="","",今日-J51),"")</f>
         <v/>
       </c>
       <c r="L51" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H51="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H51)))&gt;0,AND(ISNUMBER(K51),K51&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M51" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H51="","○ 未填",IF(ISNUMBER(SEARCH("解除",H51)),"○ 結束",IF(AND(ISNUMBER(K51),K51&gt;30),"● 紅",IF(L51=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N51" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H51)),AND(ISNUMBER(K51),K51&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42203,19 +42187,19 @@
       <c r="I52" s="14" t="n"/>
       <c r="J52" s="45" t="n"/>
       <c r="K52" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J52="","",今日-J52),"")</f>
         <v/>
       </c>
       <c r="L52" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H52="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H52)))&gt;0,AND(ISNUMBER(K52),K52&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M52" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H52="","○ 未填",IF(ISNUMBER(SEARCH("解除",H52)),"○ 結束",IF(AND(ISNUMBER(K52),K52&gt;30),"● 紅",IF(L52=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N52" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H52)),AND(ISNUMBER(K52),K52&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42231,19 +42215,19 @@
       <c r="I53" s="14" t="n"/>
       <c r="J53" s="45" t="n"/>
       <c r="K53" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J53="","",今日-J53),"")</f>
         <v/>
       </c>
       <c r="L53" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H53="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H53)))&gt;0,AND(ISNUMBER(K53),K53&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M53" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H53="","○ 未填",IF(ISNUMBER(SEARCH("解除",H53)),"○ 結束",IF(AND(ISNUMBER(K53),K53&gt;30),"● 紅",IF(L53=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N53" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H53)),AND(ISNUMBER(K53),K53&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42259,19 +42243,19 @@
       <c r="I54" s="14" t="n"/>
       <c r="J54" s="45" t="n"/>
       <c r="K54" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J54="","",今日-J54),"")</f>
         <v/>
       </c>
       <c r="L54" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H54="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H54)))&gt;0,AND(ISNUMBER(K54),K54&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M54" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H54="","○ 未填",IF(ISNUMBER(SEARCH("解除",H54)),"○ 結束",IF(AND(ISNUMBER(K54),K54&gt;30),"● 紅",IF(L54=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N54" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H54)),AND(ISNUMBER(K54),K54&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42287,19 +42271,19 @@
       <c r="I55" s="14" t="n"/>
       <c r="J55" s="45" t="n"/>
       <c r="K55" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J55="","",今日-J55),"")</f>
         <v/>
       </c>
       <c r="L55" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H55="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H55)))&gt;0,AND(ISNUMBER(K55),K55&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M55" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H55="","○ 未填",IF(ISNUMBER(SEARCH("解除",H55)),"○ 結束",IF(AND(ISNUMBER(K55),K55&gt;30),"● 紅",IF(L55=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N55" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H55)),AND(ISNUMBER(K55),K55&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42315,19 +42299,19 @@
       <c r="I56" s="14" t="n"/>
       <c r="J56" s="45" t="n"/>
       <c r="K56" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J56="","",今日-J56),"")</f>
         <v/>
       </c>
       <c r="L56" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H56="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H56)))&gt;0,AND(ISNUMBER(K56),K56&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M56" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H56="","○ 未填",IF(ISNUMBER(SEARCH("解除",H56)),"○ 結束",IF(AND(ISNUMBER(K56),K56&gt;30),"● 紅",IF(L56=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N56" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H56)),AND(ISNUMBER(K56),K56&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42343,19 +42327,19 @@
       <c r="I57" s="14" t="n"/>
       <c r="J57" s="45" t="n"/>
       <c r="K57" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J57="","",今日-J57),"")</f>
         <v/>
       </c>
       <c r="L57" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H57="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H57)))&gt;0,AND(ISNUMBER(K57),K57&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M57" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H57="","○ 未填",IF(ISNUMBER(SEARCH("解除",H57)),"○ 結束",IF(AND(ISNUMBER(K57),K57&gt;30),"● 紅",IF(L57=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N57" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H57)),AND(ISNUMBER(K57),K57&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42371,19 +42355,19 @@
       <c r="I58" s="14" t="n"/>
       <c r="J58" s="45" t="n"/>
       <c r="K58" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J58="","",今日-J58),"")</f>
         <v/>
       </c>
       <c r="L58" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H58="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H58)))&gt;0,AND(ISNUMBER(K58),K58&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M58" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H58="","○ 未填",IF(ISNUMBER(SEARCH("解除",H58)),"○ 結束",IF(AND(ISNUMBER(K58),K58&gt;30),"● 紅",IF(L58=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N58" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H58)),AND(ISNUMBER(K58),K58&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42399,19 +42383,19 @@
       <c r="I59" s="14" t="n"/>
       <c r="J59" s="45" t="n"/>
       <c r="K59" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J59="","",今日-J59),"")</f>
         <v/>
       </c>
       <c r="L59" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H59="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H59)))&gt;0,AND(ISNUMBER(K59),K59&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M59" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H59="","○ 未填",IF(ISNUMBER(SEARCH("解除",H59)),"○ 結束",IF(AND(ISNUMBER(K59),K59&gt;30),"● 紅",IF(L59=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N59" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H59)),AND(ISNUMBER(K59),K59&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42427,19 +42411,19 @@
       <c r="I60" s="14" t="n"/>
       <c r="J60" s="45" t="n"/>
       <c r="K60" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J60="","",今日-J60),"")</f>
         <v/>
       </c>
       <c r="L60" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H60="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H60)))&gt;0,AND(ISNUMBER(K60),K60&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M60" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H60="","○ 未填",IF(ISNUMBER(SEARCH("解除",H60)),"○ 結束",IF(AND(ISNUMBER(K60),K60&gt;30),"● 紅",IF(L60=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N60" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H60)),AND(ISNUMBER(K60),K60&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42455,19 +42439,19 @@
       <c r="I61" s="14" t="n"/>
       <c r="J61" s="45" t="n"/>
       <c r="K61" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J61="","",今日-J61),"")</f>
         <v/>
       </c>
       <c r="L61" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H61="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H61)))&gt;0,AND(ISNUMBER(K61),K61&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M61" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H61="","○ 未填",IF(ISNUMBER(SEARCH("解除",H61)),"○ 結束",IF(AND(ISNUMBER(K61),K61&gt;30),"● 紅",IF(L61=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N61" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H61)),AND(ISNUMBER(K61),K61&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42483,19 +42467,19 @@
       <c r="I62" s="14" t="n"/>
       <c r="J62" s="45" t="n"/>
       <c r="K62" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J62="","",今日-J62),"")</f>
         <v/>
       </c>
       <c r="L62" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H62="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H62)))&gt;0,AND(ISNUMBER(K62),K62&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M62" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H62="","○ 未填",IF(ISNUMBER(SEARCH("解除",H62)),"○ 結束",IF(AND(ISNUMBER(K62),K62&gt;30),"● 紅",IF(L62=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N62" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H62)),AND(ISNUMBER(K62),K62&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42511,19 +42495,19 @@
       <c r="I63" s="14" t="n"/>
       <c r="J63" s="45" t="n"/>
       <c r="K63" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J63="","",今日-J63),"")</f>
         <v/>
       </c>
       <c r="L63" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H63="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H63)))&gt;0,AND(ISNUMBER(K63),K63&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M63" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H63="","○ 未填",IF(ISNUMBER(SEARCH("解除",H63)),"○ 結束",IF(AND(ISNUMBER(K63),K63&gt;30),"● 紅",IF(L63=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N63" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H63)),AND(ISNUMBER(K63),K63&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42539,19 +42523,19 @@
       <c r="I64" s="14" t="n"/>
       <c r="J64" s="45" t="n"/>
       <c r="K64" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J64="","",今日-J64),"")</f>
         <v/>
       </c>
       <c r="L64" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H64="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H64)))&gt;0,AND(ISNUMBER(K64),K64&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M64" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H64="","○ 未填",IF(ISNUMBER(SEARCH("解除",H64)),"○ 結束",IF(AND(ISNUMBER(K64),K64&gt;30),"● 紅",IF(L64=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N64" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H64)),AND(ISNUMBER(K64),K64&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42567,19 +42551,19 @@
       <c r="I65" s="14" t="n"/>
       <c r="J65" s="45" t="n"/>
       <c r="K65" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J65="","",今日-J65),"")</f>
         <v/>
       </c>
       <c r="L65" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H65="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H65)))&gt;0,AND(ISNUMBER(K65),K65&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M65" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H65="","○ 未填",IF(ISNUMBER(SEARCH("解除",H65)),"○ 結束",IF(AND(ISNUMBER(K65),K65&gt;30),"● 紅",IF(L65=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N65" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H65)),AND(ISNUMBER(K65),K65&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42595,19 +42579,19 @@
       <c r="I66" s="14" t="n"/>
       <c r="J66" s="45" t="n"/>
       <c r="K66" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J66="","",今日-J66),"")</f>
         <v/>
       </c>
       <c r="L66" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H66="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H66)))&gt;0,AND(ISNUMBER(K66),K66&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M66" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H66="","○ 未填",IF(ISNUMBER(SEARCH("解除",H66)),"○ 結束",IF(AND(ISNUMBER(K66),K66&gt;30),"● 紅",IF(L66=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N66" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H66)),AND(ISNUMBER(K66),K66&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42623,19 +42607,19 @@
       <c r="I67" s="14" t="n"/>
       <c r="J67" s="45" t="n"/>
       <c r="K67" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J67="","",今日-J67),"")</f>
         <v/>
       </c>
       <c r="L67" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H67="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H67)))&gt;0,AND(ISNUMBER(K67),K67&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M67" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H67="","○ 未填",IF(ISNUMBER(SEARCH("解除",H67)),"○ 結束",IF(AND(ISNUMBER(K67),K67&gt;30),"● 紅",IF(L67=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N67" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H67)),AND(ISNUMBER(K67),K67&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42651,19 +42635,19 @@
       <c r="I68" s="14" t="n"/>
       <c r="J68" s="45" t="n"/>
       <c r="K68" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J68="","",今日-J68),"")</f>
         <v/>
       </c>
       <c r="L68" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H68="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H68)))&gt;0,AND(ISNUMBER(K68),K68&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M68" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H68="","○ 未填",IF(ISNUMBER(SEARCH("解除",H68)),"○ 結束",IF(AND(ISNUMBER(K68),K68&gt;30),"● 紅",IF(L68=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N68" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H68)),AND(ISNUMBER(K68),K68&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42679,19 +42663,19 @@
       <c r="I69" s="14" t="n"/>
       <c r="J69" s="45" t="n"/>
       <c r="K69" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J69="","",今日-J69),"")</f>
         <v/>
       </c>
       <c r="L69" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H69="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H69)))&gt;0,AND(ISNUMBER(K69),K69&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M69" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H69="","○ 未填",IF(ISNUMBER(SEARCH("解除",H69)),"○ 結束",IF(AND(ISNUMBER(K69),K69&gt;30),"● 紅",IF(L69=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N69" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H69)),AND(ISNUMBER(K69),K69&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42707,19 +42691,19 @@
       <c r="I70" s="14" t="n"/>
       <c r="J70" s="45" t="n"/>
       <c r="K70" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J70="","",今日-J70),"")</f>
         <v/>
       </c>
       <c r="L70" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H70="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H70)))&gt;0,AND(ISNUMBER(K70),K70&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M70" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H70="","○ 未填",IF(ISNUMBER(SEARCH("解除",H70)),"○ 結束",IF(AND(ISNUMBER(K70),K70&gt;30),"● 紅",IF(L70=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N70" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H70)),AND(ISNUMBER(K70),K70&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42735,19 +42719,19 @@
       <c r="I71" s="14" t="n"/>
       <c r="J71" s="45" t="n"/>
       <c r="K71" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J71="","",今日-J71),"")</f>
         <v/>
       </c>
       <c r="L71" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H71="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H71)))&gt;0,AND(ISNUMBER(K71),K71&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M71" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H71="","○ 未填",IF(ISNUMBER(SEARCH("解除",H71)),"○ 結束",IF(AND(ISNUMBER(K71),K71&gt;30),"● 紅",IF(L71=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N71" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H71)),AND(ISNUMBER(K71),K71&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42763,19 +42747,19 @@
       <c r="I72" s="14" t="n"/>
       <c r="J72" s="45" t="n"/>
       <c r="K72" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J72="","",今日-J72),"")</f>
         <v/>
       </c>
       <c r="L72" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H72="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H72)))&gt;0,AND(ISNUMBER(K72),K72&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M72" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H72="","○ 未填",IF(ISNUMBER(SEARCH("解除",H72)),"○ 結束",IF(AND(ISNUMBER(K72),K72&gt;30),"● 紅",IF(L72=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N72" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H72)),AND(ISNUMBER(K72),K72&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42791,19 +42775,19 @@
       <c r="I73" s="14" t="n"/>
       <c r="J73" s="45" t="n"/>
       <c r="K73" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J73="","",今日-J73),"")</f>
         <v/>
       </c>
       <c r="L73" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H73="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H73)))&gt;0,AND(ISNUMBER(K73),K73&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M73" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H73="","○ 未填",IF(ISNUMBER(SEARCH("解除",H73)),"○ 結束",IF(AND(ISNUMBER(K73),K73&gt;30),"● 紅",IF(L73=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N73" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H73)),AND(ISNUMBER(K73),K73&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42819,19 +42803,19 @@
       <c r="I74" s="14" t="n"/>
       <c r="J74" s="45" t="n"/>
       <c r="K74" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J74="","",今日-J74),"")</f>
         <v/>
       </c>
       <c r="L74" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H74="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H74)))&gt;0,AND(ISNUMBER(K74),K74&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M74" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H74="","○ 未填",IF(ISNUMBER(SEARCH("解除",H74)),"○ 結束",IF(AND(ISNUMBER(K74),K74&gt;30),"● 紅",IF(L74=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N74" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H74)),AND(ISNUMBER(K74),K74&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42847,19 +42831,19 @@
       <c r="I75" s="14" t="n"/>
       <c r="J75" s="45" t="n"/>
       <c r="K75" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J75="","",今日-J75),"")</f>
         <v/>
       </c>
       <c r="L75" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H75="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H75)))&gt;0,AND(ISNUMBER(K75),K75&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M75" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H75="","○ 未填",IF(ISNUMBER(SEARCH("解除",H75)),"○ 結束",IF(AND(ISNUMBER(K75),K75&gt;30),"● 紅",IF(L75=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N75" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H75)),AND(ISNUMBER(K75),K75&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42875,19 +42859,19 @@
       <c r="I76" s="14" t="n"/>
       <c r="J76" s="45" t="n"/>
       <c r="K76" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J76="","",今日-J76),"")</f>
         <v/>
       </c>
       <c r="L76" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H76="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H76)))&gt;0,AND(ISNUMBER(K76),K76&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M76" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H76="","○ 未填",IF(ISNUMBER(SEARCH("解除",H76)),"○ 結束",IF(AND(ISNUMBER(K76),K76&gt;30),"● 紅",IF(L76=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N76" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H76)),AND(ISNUMBER(K76),K76&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42903,19 +42887,19 @@
       <c r="I77" s="14" t="n"/>
       <c r="J77" s="45" t="n"/>
       <c r="K77" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J77="","",今日-J77),"")</f>
         <v/>
       </c>
       <c r="L77" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H77="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H77)))&gt;0,AND(ISNUMBER(K77),K77&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M77" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H77="","○ 未填",IF(ISNUMBER(SEARCH("解除",H77)),"○ 結束",IF(AND(ISNUMBER(K77),K77&gt;30),"● 紅",IF(L77=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N77" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H77)),AND(ISNUMBER(K77),K77&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42931,19 +42915,19 @@
       <c r="I78" s="14" t="n"/>
       <c r="J78" s="45" t="n"/>
       <c r="K78" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J78="","",今日-J78),"")</f>
         <v/>
       </c>
       <c r="L78" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H78="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H78)))&gt;0,AND(ISNUMBER(K78),K78&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M78" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H78="","○ 未填",IF(ISNUMBER(SEARCH("解除",H78)),"○ 結束",IF(AND(ISNUMBER(K78),K78&gt;30),"● 紅",IF(L78=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N78" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H78)),AND(ISNUMBER(K78),K78&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42959,19 +42943,19 @@
       <c r="I79" s="14" t="n"/>
       <c r="J79" s="45" t="n"/>
       <c r="K79" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J79="","",今日-J79),"")</f>
         <v/>
       </c>
       <c r="L79" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H79="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H79)))&gt;0,AND(ISNUMBER(K79),K79&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M79" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H79="","○ 未填",IF(ISNUMBER(SEARCH("解除",H79)),"○ 結束",IF(AND(ISNUMBER(K79),K79&gt;30),"● 紅",IF(L79=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N79" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H79)),AND(ISNUMBER(K79),K79&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -42987,19 +42971,19 @@
       <c r="I80" s="14" t="n"/>
       <c r="J80" s="45" t="n"/>
       <c r="K80" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J80="","",今日-J80),"")</f>
         <v/>
       </c>
       <c r="L80" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H80="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H80)))&gt;0,AND(ISNUMBER(K80),K80&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M80" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H80="","○ 未填",IF(ISNUMBER(SEARCH("解除",H80)),"○ 結束",IF(AND(ISNUMBER(K80),K80&gt;30),"● 紅",IF(L80=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N80" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H80)),AND(ISNUMBER(K80),K80&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -43015,19 +42999,19 @@
       <c r="I81" s="14" t="n"/>
       <c r="J81" s="45" t="n"/>
       <c r="K81" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J81="","",今日-J81),"")</f>
         <v/>
       </c>
       <c r="L81" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H81="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H81)))&gt;0,AND(ISNUMBER(K81),K81&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M81" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H81="","○ 未填",IF(ISNUMBER(SEARCH("解除",H81)),"○ 結束",IF(AND(ISNUMBER(K81),K81&gt;30),"● 紅",IF(L81=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N81" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H81)),AND(ISNUMBER(K81),K81&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -43043,19 +43027,19 @@
       <c r="I82" s="14" t="n"/>
       <c r="J82" s="45" t="n"/>
       <c r="K82" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J82="","",今日-J82),"")</f>
         <v/>
       </c>
       <c r="L82" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H82="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H82)))&gt;0,AND(ISNUMBER(K82),K82&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M82" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H82="","○ 未填",IF(ISNUMBER(SEARCH("解除",H82)),"○ 結束",IF(AND(ISNUMBER(K82),K82&gt;30),"● 紅",IF(L82=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N82" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H82)),AND(ISNUMBER(K82),K82&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -43071,19 +43055,19 @@
       <c r="I83" s="14" t="n"/>
       <c r="J83" s="45" t="n"/>
       <c r="K83" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J83="","",今日-J83),"")</f>
         <v/>
       </c>
       <c r="L83" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H83="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H83)))&gt;0,AND(ISNUMBER(K83),K83&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M83" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H83="","○ 未填",IF(ISNUMBER(SEARCH("解除",H83)),"○ 結束",IF(AND(ISNUMBER(K83),K83&gt;30),"● 紅",IF(L83=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N83" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H83)),AND(ISNUMBER(K83),K83&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>
@@ -43099,19 +43083,19 @@
       <c r="I84" s="14" t="n"/>
       <c r="J84" s="45" t="n"/>
       <c r="K84" s="141">
-        <f>IFERROR(IF([@最後到驗日]="","",今日-[@最後到驗日]),"")</f>
+        <f>IFERROR(IF(J84="","",今日-J84),"")</f>
         <v/>
       </c>
       <c r="L84" s="141">
-        <f>IFERROR(IF([@管制情形]="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},[@管制情形])))&gt;0,AND(ISNUMBER([@距今天數]),[@距今天數]&lt;=30)),1,0)),0)</f>
+        <f>IFERROR(IF(H84="",0,IF(OR(SUMPRODUCT(--ISNUMBER(SEARCH({"已驗","已到驗","通緝","強採","在監"},H84)))&gt;0,AND(ISNUMBER(K84),K84&lt;=30)),1,0)),0)</f>
         <v/>
       </c>
       <c r="M84" s="15">
-        <f>IFERROR(IF([@管制情形]="","○ 未填",IF(ISNUMBER(SEARCH("解除",[@管制情形])),"○ 結束",IF(AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30),"● 紅",IF([@是否到驗]=1,"● 綠","⚠ 黃")))),"")</f>
+        <f>IFERROR(IF(H84="","○ 未填",IF(ISNUMBER(SEARCH("解除",H84)),"○ 結束",IF(AND(ISNUMBER(K84),K84&gt;30),"● 紅",IF(L84=1,"● 綠","⚠ 黃")))),"")</f>
         <v/>
       </c>
       <c r="N84" s="141">
-        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",[@管制情形])),AND(ISNUMBER([@距今天數]),[@距今天數]&gt;30)),1,0),0)</f>
+        <f>IFERROR(IF(OR(ISNUMBER(SEARCH("未到驗",H84)),AND(ISNUMBER(K84),K84&gt;30)),1,0),0)</f>
         <v/>
       </c>
     </row>

--- a/build/output/PoliceStation_v2.2_部署版.xlsx
+++ b/build/output/PoliceStation_v2.2_部署版.xlsx
@@ -25274,7 +25274,7 @@
         <v/>
       </c>
       <c r="L15" s="15">
-        <f>IFERROR(IF(OR(T15&lt;&gt;"",J15="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T15="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M15" s="226" t="n"/>
@@ -25315,7 +25315,7 @@
         <v/>
       </c>
       <c r="L16" s="15">
-        <f>IFERROR(IF(OR(T16&lt;&gt;"",J16="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T16="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M16" s="226" t="n"/>
@@ -25356,7 +25356,7 @@
         <v/>
       </c>
       <c r="L17" s="15">
-        <f>IFERROR(IF(OR(T17&lt;&gt;"",J17="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T17="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M17" s="226" t="n"/>
@@ -25397,7 +25397,7 @@
         <v/>
       </c>
       <c r="L18" s="15">
-        <f>IFERROR(IF(OR(T18&lt;&gt;"",J18="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T18="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M18" s="226" t="n"/>
@@ -25438,7 +25438,7 @@
         <v/>
       </c>
       <c r="L19" s="15">
-        <f>IFERROR(IF(OR(T19&lt;&gt;"",J19="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T19="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M19" s="228" t="n"/>
@@ -25479,7 +25479,7 @@
         <v/>
       </c>
       <c r="L20" s="15">
-        <f>IFERROR(IF(OR(T20&lt;&gt;"",J20="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T20="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M20" s="228" t="n"/>
@@ -25520,7 +25520,7 @@
         <v/>
       </c>
       <c r="L21" s="15">
-        <f>IFERROR(IF(OR(T21&lt;&gt;"",J21="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T21="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M21" s="228" t="n"/>
@@ -25561,7 +25561,7 @@
         <v/>
       </c>
       <c r="L22" s="15">
-        <f>IFERROR(IF(OR(T22&lt;&gt;"",J22="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T22="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M22" s="228" t="n"/>
@@ -25602,7 +25602,7 @@
         <v/>
       </c>
       <c r="L23" s="15">
-        <f>IFERROR(IF(OR(T23&lt;&gt;"",J23="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T23="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M23" s="228" t="n"/>
@@ -25643,7 +25643,7 @@
         <v/>
       </c>
       <c r="L24" s="15">
-        <f>IFERROR(IF(OR(T24&lt;&gt;"",J24="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T24="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M24" s="228" t="n"/>
@@ -25684,7 +25684,7 @@
         <v/>
       </c>
       <c r="L25" s="15">
-        <f>IFERROR(IF(OR(T25&lt;&gt;"",J25="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T25="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M25" s="228" t="n"/>
@@ -25725,7 +25725,7 @@
         <v/>
       </c>
       <c r="L26" s="15">
-        <f>IFERROR(IF(OR(T26&lt;&gt;"",J26="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T26="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M26" s="228" t="n"/>
@@ -25766,7 +25766,7 @@
         <v/>
       </c>
       <c r="L27" s="15">
-        <f>IFERROR(IF(OR(T27&lt;&gt;"",J27="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T27="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M27" s="228" t="n"/>
@@ -25807,7 +25807,7 @@
         <v/>
       </c>
       <c r="L28" s="15">
-        <f>IFERROR(IF(OR(T28&lt;&gt;"",J28="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T28="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M28" s="228" t="n"/>
@@ -25848,7 +25848,7 @@
         <v/>
       </c>
       <c r="L29" s="15">
-        <f>IFERROR(IF(OR(T29&lt;&gt;"",J29="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T29="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M29" s="228" t="n"/>
@@ -25889,7 +25889,7 @@
         <v/>
       </c>
       <c r="L30" s="15">
-        <f>IFERROR(IF(OR(T30&lt;&gt;"",J30="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T30="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M30" s="228" t="n"/>
@@ -25930,7 +25930,7 @@
         <v/>
       </c>
       <c r="L31" s="15">
-        <f>IFERROR(IF(OR(T31&lt;&gt;"",J31="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T31="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M31" s="228" t="n"/>
@@ -25971,7 +25971,7 @@
         <v/>
       </c>
       <c r="L32" s="15">
-        <f>IFERROR(IF(OR(T32&lt;&gt;"",J32="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T32="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M32" s="228" t="n"/>
@@ -26012,7 +26012,7 @@
         <v/>
       </c>
       <c r="L33" s="15">
-        <f>IFERROR(IF(OR(T33&lt;&gt;"",J33="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T33="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M33" s="228" t="n"/>
@@ -26053,7 +26053,7 @@
         <v/>
       </c>
       <c r="L34" s="15">
-        <f>IFERROR(IF(OR(T34&lt;&gt;"",J34="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T34="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M34" s="228" t="n"/>
@@ -26094,7 +26094,7 @@
         <v/>
       </c>
       <c r="L35" s="15">
-        <f>IFERROR(IF(OR(T35&lt;&gt;"",J35="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T35="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M35" s="228" t="n"/>
@@ -26135,7 +26135,7 @@
         <v/>
       </c>
       <c r="L36" s="15">
-        <f>IFERROR(IF(OR(T36&lt;&gt;"",J36="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T36="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M36" s="228" t="n"/>
@@ -26176,7 +26176,7 @@
         <v/>
       </c>
       <c r="L37" s="15">
-        <f>IFERROR(IF(OR(T37&lt;&gt;"",J37="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T37="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M37" s="228" t="n"/>
@@ -26217,7 +26217,7 @@
         <v/>
       </c>
       <c r="L38" s="15">
-        <f>IFERROR(IF(OR(T38&lt;&gt;"",J38="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T38="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M38" s="228" t="n"/>
@@ -26258,7 +26258,7 @@
         <v/>
       </c>
       <c r="L39" s="15">
-        <f>IFERROR(IF(OR(T39&lt;&gt;"",J39="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T39="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M39" s="228" t="n"/>
@@ -26299,7 +26299,7 @@
         <v/>
       </c>
       <c r="L40" s="15">
-        <f>IFERROR(IF(OR(T40&lt;&gt;"",J40="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T40="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M40" s="228" t="n"/>
@@ -26340,7 +26340,7 @@
         <v/>
       </c>
       <c r="L41" s="15">
-        <f>IFERROR(IF(OR(T41&lt;&gt;"",J41="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T41="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M41" s="228" t="n"/>
@@ -26381,7 +26381,7 @@
         <v/>
       </c>
       <c r="L42" s="15">
-        <f>IFERROR(IF(OR(T42&lt;&gt;"",J42="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T42="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M42" s="228" t="n"/>
@@ -26422,7 +26422,7 @@
         <v/>
       </c>
       <c r="L43" s="15">
-        <f>IFERROR(IF(OR(T43&lt;&gt;"",J43="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T43="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M43" s="228" t="n"/>
@@ -26463,7 +26463,7 @@
         <v/>
       </c>
       <c r="L44" s="15">
-        <f>IFERROR(IF(OR(T44&lt;&gt;"",J44="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T44="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M44" s="228" t="n"/>
@@ -26504,7 +26504,7 @@
         <v/>
       </c>
       <c r="L45" s="15">
-        <f>IFERROR(IF(OR(T45&lt;&gt;"",J45="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T45="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M45" s="228" t="n"/>
@@ -26545,7 +26545,7 @@
         <v/>
       </c>
       <c r="L46" s="15">
-        <f>IFERROR(IF(OR(T46&lt;&gt;"",J46="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T46="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M46" s="228" t="n"/>
@@ -26586,7 +26586,7 @@
         <v/>
       </c>
       <c r="L47" s="15">
-        <f>IFERROR(IF(OR(T47&lt;&gt;"",J47="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T47="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M47" s="228" t="n"/>
@@ -26627,7 +26627,7 @@
         <v/>
       </c>
       <c r="L48" s="15">
-        <f>IFERROR(IF(OR(T48&lt;&gt;"",J48="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T48="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M48" s="228" t="n"/>
@@ -26668,7 +26668,7 @@
         <v/>
       </c>
       <c r="L49" s="15">
-        <f>IFERROR(IF(OR(T49&lt;&gt;"",J49="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T49="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M49" s="228" t="n"/>
@@ -26709,7 +26709,7 @@
         <v/>
       </c>
       <c r="L50" s="15">
-        <f>IFERROR(IF(OR(T50&lt;&gt;"",J50="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T50="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M50" s="228" t="n"/>
@@ -26750,7 +26750,7 @@
         <v/>
       </c>
       <c r="L51" s="15">
-        <f>IFERROR(IF(OR(T51&lt;&gt;"",J51="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T51="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M51" s="228" t="n"/>
@@ -26791,7 +26791,7 @@
         <v/>
       </c>
       <c r="L52" s="15">
-        <f>IFERROR(IF(OR(T52&lt;&gt;"",J52="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T52="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M52" s="228" t="n"/>
@@ -26832,7 +26832,7 @@
         <v/>
       </c>
       <c r="L53" s="15">
-        <f>IFERROR(IF(OR(T53&lt;&gt;"",J53="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T53="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M53" s="228" t="n"/>
@@ -26873,7 +26873,7 @@
         <v/>
       </c>
       <c r="L54" s="15">
-        <f>IFERROR(IF(OR(T54&lt;&gt;"",J54="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T54="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M54" s="228" t="n"/>
@@ -26914,7 +26914,7 @@
         <v/>
       </c>
       <c r="L55" s="15">
-        <f>IFERROR(IF(OR(T55&lt;&gt;"",J55="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T55="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M55" s="228" t="n"/>
@@ -26955,7 +26955,7 @@
         <v/>
       </c>
       <c r="L56" s="15">
-        <f>IFERROR(IF(OR(T56&lt;&gt;"",J56="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T56="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M56" s="228" t="n"/>
@@ -26996,7 +26996,7 @@
         <v/>
       </c>
       <c r="L57" s="15">
-        <f>IFERROR(IF(OR(T57&lt;&gt;"",J57="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T57="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M57" s="228" t="n"/>
@@ -27037,7 +27037,7 @@
         <v/>
       </c>
       <c r="L58" s="15">
-        <f>IFERROR(IF(OR(T58&lt;&gt;"",J58="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T58="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M58" s="228" t="n"/>
@@ -27078,7 +27078,7 @@
         <v/>
       </c>
       <c r="L59" s="15">
-        <f>IFERROR(IF(OR(T59&lt;&gt;"",J59="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T59="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M59" s="228" t="n"/>
@@ -27119,7 +27119,7 @@
         <v/>
       </c>
       <c r="L60" s="15">
-        <f>IFERROR(IF(OR(T60&lt;&gt;"",J60="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T60="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M60" s="228" t="n"/>
@@ -27160,7 +27160,7 @@
         <v/>
       </c>
       <c r="L61" s="15">
-        <f>IFERROR(IF(OR(T61&lt;&gt;"",J61="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T61="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M61" s="228" t="n"/>
@@ -27201,7 +27201,7 @@
         <v/>
       </c>
       <c r="L62" s="15">
-        <f>IFERROR(IF(OR(T62&lt;&gt;"",J62="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T62="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M62" s="228" t="n"/>
@@ -27242,7 +27242,7 @@
         <v/>
       </c>
       <c r="L63" s="15">
-        <f>IFERROR(IF(OR(T63&lt;&gt;"",J63="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T63="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M63" s="228" t="n"/>
@@ -27283,7 +27283,7 @@
         <v/>
       </c>
       <c r="L64" s="15">
-        <f>IFERROR(IF(OR(T64&lt;&gt;"",J64="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T64="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M64" s="228" t="n"/>
@@ -27324,7 +27324,7 @@
         <v/>
       </c>
       <c r="L65" s="15">
-        <f>IFERROR(IF(OR(T65&lt;&gt;"",J65="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T65="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M65" s="228" t="n"/>
@@ -27365,7 +27365,7 @@
         <v/>
       </c>
       <c r="L66" s="15">
-        <f>IFERROR(IF(OR(T66&lt;&gt;"",J66="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T66="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M66" s="228" t="n"/>
@@ -27406,7 +27406,7 @@
         <v/>
       </c>
       <c r="L67" s="15">
-        <f>IFERROR(IF(OR(T67&lt;&gt;"",J67="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T67="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M67" s="228" t="n"/>
@@ -27447,7 +27447,7 @@
         <v/>
       </c>
       <c r="L68" s="15">
-        <f>IFERROR(IF(OR(T68&lt;&gt;"",J68="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T68="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M68" s="228" t="n"/>
@@ -27488,7 +27488,7 @@
         <v/>
       </c>
       <c r="L69" s="15">
-        <f>IFERROR(IF(OR(T69&lt;&gt;"",J69="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T69="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M69" s="228" t="n"/>
@@ -27529,7 +27529,7 @@
         <v/>
       </c>
       <c r="L70" s="15">
-        <f>IFERROR(IF(OR(T70&lt;&gt;"",J70="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T70="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M70" s="228" t="n"/>
@@ -27570,7 +27570,7 @@
         <v/>
       </c>
       <c r="L71" s="15">
-        <f>IFERROR(IF(OR(T71&lt;&gt;"",J71="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T71="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M71" s="228" t="n"/>
@@ -27611,7 +27611,7 @@
         <v/>
       </c>
       <c r="L72" s="15">
-        <f>IFERROR(IF(OR(T72&lt;&gt;"",J72="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T72="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M72" s="228" t="n"/>
@@ -27652,7 +27652,7 @@
         <v/>
       </c>
       <c r="L73" s="15">
-        <f>IFERROR(IF(OR(T73&lt;&gt;"",J73="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T73="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M73" s="228" t="n"/>
@@ -27693,7 +27693,7 @@
         <v/>
       </c>
       <c r="L74" s="15">
-        <f>IFERROR(IF(OR(T74&lt;&gt;"",J74="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T74="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M74" s="228" t="n"/>
@@ -27734,7 +27734,7 @@
         <v/>
       </c>
       <c r="L75" s="15">
-        <f>IFERROR(IF(OR(T75&lt;&gt;"",J75="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T75="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M75" s="228" t="n"/>
@@ -27775,7 +27775,7 @@
         <v/>
       </c>
       <c r="L76" s="15">
-        <f>IFERROR(IF(OR(T76&lt;&gt;"",J76="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T76="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M76" s="228" t="n"/>
@@ -27816,7 +27816,7 @@
         <v/>
       </c>
       <c r="L77" s="15">
-        <f>IFERROR(IF(OR(T77&lt;&gt;"",J77="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T77="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M77" s="228" t="n"/>
@@ -27857,7 +27857,7 @@
         <v/>
       </c>
       <c r="L78" s="15">
-        <f>IFERROR(IF(OR(T78&lt;&gt;"",J78="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T78="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M78" s="228" t="n"/>
@@ -27898,7 +27898,7 @@
         <v/>
       </c>
       <c r="L79" s="15">
-        <f>IFERROR(IF(OR(T79&lt;&gt;"",J79="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T79="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M79" s="228" t="n"/>
@@ -27939,7 +27939,7 @@
         <v/>
       </c>
       <c r="L80" s="15">
-        <f>IFERROR(IF(OR(T80&lt;&gt;"",J80="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T80="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M80" s="228" t="n"/>
@@ -27980,7 +27980,7 @@
         <v/>
       </c>
       <c r="L81" s="15">
-        <f>IFERROR(IF(OR(T81&lt;&gt;"",J81="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T81="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M81" s="228" t="n"/>
@@ -28021,7 +28021,7 @@
         <v/>
       </c>
       <c r="L82" s="15">
-        <f>IFERROR(IF(OR(T82&lt;&gt;"",J82="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T82="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M82" s="228" t="n"/>
@@ -28062,7 +28062,7 @@
         <v/>
       </c>
       <c r="L83" s="15">
-        <f>IFERROR(IF(OR(T83&lt;&gt;"",J83="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T83="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M83" s="228" t="n"/>
@@ -28103,7 +28103,7 @@
         <v/>
       </c>
       <c r="L84" s="15">
-        <f>IFERROR(IF(OR(T84&lt;&gt;"",J84="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T84="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M84" s="228" t="n"/>
@@ -28144,7 +28144,7 @@
         <v/>
       </c>
       <c r="L85" s="15">
-        <f>IFERROR(IF(OR(T85&lt;&gt;"",J85="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T85="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M85" s="228" t="n"/>
@@ -28185,7 +28185,7 @@
         <v/>
       </c>
       <c r="L86" s="15">
-        <f>IFERROR(IF(OR(T86&lt;&gt;"",J86="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T86="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M86" s="228" t="n"/>
@@ -28226,7 +28226,7 @@
         <v/>
       </c>
       <c r="L87" s="15">
-        <f>IFERROR(IF(OR(T87&lt;&gt;"",J87="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T87="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M87" s="228" t="n"/>
@@ -28267,7 +28267,7 @@
         <v/>
       </c>
       <c r="L88" s="15">
-        <f>IFERROR(IF(OR(T88&lt;&gt;"",J88="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T88="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M88" s="228" t="n"/>
@@ -28308,7 +28308,7 @@
         <v/>
       </c>
       <c r="L89" s="15">
-        <f>IFERROR(IF(OR(T89&lt;&gt;"",J89="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T89="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M89" s="228" t="n"/>
@@ -28349,7 +28349,7 @@
         <v/>
       </c>
       <c r="L90" s="15">
-        <f>IFERROR(IF(OR(T90&lt;&gt;"",J90="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T90="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M90" s="228" t="n"/>
@@ -28390,7 +28390,7 @@
         <v/>
       </c>
       <c r="L91" s="15">
-        <f>IFERROR(IF(OR(T91&lt;&gt;"",J91="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T91="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M91" s="228" t="n"/>
@@ -28431,7 +28431,7 @@
         <v/>
       </c>
       <c r="L92" s="15">
-        <f>IFERROR(IF(OR(T92&lt;&gt;"",J92="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T92="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M92" s="228" t="n"/>
@@ -28472,7 +28472,7 @@
         <v/>
       </c>
       <c r="L93" s="15">
-        <f>IFERROR(IF(OR(T93&lt;&gt;"",J93="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T93="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M93" s="228" t="n"/>
@@ -28513,7 +28513,7 @@
         <v/>
       </c>
       <c r="L94" s="15">
-        <f>IFERROR(IF(OR(T94&lt;&gt;"",J94="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T94="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M94" s="228" t="n"/>
@@ -28554,7 +28554,7 @@
         <v/>
       </c>
       <c r="L95" s="15">
-        <f>IFERROR(IF(OR(T95&lt;&gt;"",J95="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T95="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M95" s="228" t="n"/>
@@ -28595,7 +28595,7 @@
         <v/>
       </c>
       <c r="L96" s="15">
-        <f>IFERROR(IF(OR(T96&lt;&gt;"",J96="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T96="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M96" s="228" t="n"/>
@@ -28636,7 +28636,7 @@
         <v/>
       </c>
       <c r="L97" s="15">
-        <f>IFERROR(IF(OR(T97&lt;&gt;"",J97="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T97="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M97" s="228" t="n"/>
@@ -28677,7 +28677,7 @@
         <v/>
       </c>
       <c r="L98" s="15">
-        <f>IFERROR(IF(OR(T98&lt;&gt;"",J98="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T98="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M98" s="228" t="n"/>
@@ -28718,7 +28718,7 @@
         <v/>
       </c>
       <c r="L99" s="15">
-        <f>IFERROR(IF(OR(T99&lt;&gt;"",J99="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T99="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M99" s="228" t="n"/>
@@ -28759,7 +28759,7 @@
         <v/>
       </c>
       <c r="L100" s="15">
-        <f>IFERROR(IF(OR(T100&lt;&gt;"",J100="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T100="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M100" s="228" t="n"/>
@@ -28800,7 +28800,7 @@
         <v/>
       </c>
       <c r="L101" s="15">
-        <f>IFERROR(IF(OR(T101&lt;&gt;"",J101="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T101="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M101" s="228" t="n"/>
@@ -28841,7 +28841,7 @@
         <v/>
       </c>
       <c r="L102" s="15">
-        <f>IFERROR(IF(OR(T102&lt;&gt;"",J102="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T102="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M102" s="228" t="n"/>
@@ -28882,7 +28882,7 @@
         <v/>
       </c>
       <c r="L103" s="15">
-        <f>IFERROR(IF(OR(T103&lt;&gt;"",J103="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T103="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M103" s="228" t="n"/>
@@ -28923,7 +28923,7 @@
         <v/>
       </c>
       <c r="L104" s="15">
-        <f>IFERROR(IF(OR(T104&lt;&gt;"",J104="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T104="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M104" s="228" t="n"/>
@@ -28964,7 +28964,7 @@
         <v/>
       </c>
       <c r="L105" s="15">
-        <f>IFERROR(IF(OR(T105&lt;&gt;"",J105="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T105="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M105" s="228" t="n"/>
@@ -29005,7 +29005,7 @@
         <v/>
       </c>
       <c r="L106" s="15">
-        <f>IFERROR(IF(OR(T106&lt;&gt;"",J106="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T106="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M106" s="228" t="n"/>
@@ -29046,7 +29046,7 @@
         <v/>
       </c>
       <c r="L107" s="15">
-        <f>IFERROR(IF(OR(T107&lt;&gt;"",J107="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T107="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M107" s="228" t="n"/>
@@ -29087,7 +29087,7 @@
         <v/>
       </c>
       <c r="L108" s="15">
-        <f>IFERROR(IF(OR(T108&lt;&gt;"",J108="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T108="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M108" s="228" t="n"/>
@@ -29128,7 +29128,7 @@
         <v/>
       </c>
       <c r="L109" s="15">
-        <f>IFERROR(IF(OR(T109&lt;&gt;"",J109="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T109="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M109" s="228" t="n"/>
@@ -29169,7 +29169,7 @@
         <v/>
       </c>
       <c r="L110" s="15">
-        <f>IFERROR(IF(OR(T110&lt;&gt;"",J110="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T110="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M110" s="228" t="n"/>
@@ -29210,7 +29210,7 @@
         <v/>
       </c>
       <c r="L111" s="15">
-        <f>IFERROR(IF(OR(T111&lt;&gt;"",J111="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T111="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M111" s="228" t="n"/>
@@ -29251,7 +29251,7 @@
         <v/>
       </c>
       <c r="L112" s="15">
-        <f>IFERROR(IF(OR(T112&lt;&gt;"",J112="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T112="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M112" s="228" t="n"/>
@@ -29292,7 +29292,7 @@
         <v/>
       </c>
       <c r="L113" s="15">
-        <f>IFERROR(IF(OR(T113&lt;&gt;"",J113="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T113="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M113" s="228" t="n"/>
@@ -29333,7 +29333,7 @@
         <v/>
       </c>
       <c r="L114" s="15">
-        <f>IFERROR(IF(OR(T114&lt;&gt;"",J114="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T114="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M114" s="228" t="n"/>
@@ -29374,7 +29374,7 @@
         <v/>
       </c>
       <c r="L115" s="15">
-        <f>IFERROR(IF(OR(T115&lt;&gt;"",J115="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T115="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M115" s="228" t="n"/>
@@ -29415,7 +29415,7 @@
         <v/>
       </c>
       <c r="L116" s="15">
-        <f>IFERROR(IF(OR(T116&lt;&gt;"",J116="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T116="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M116" s="228" t="n"/>
@@ -29456,7 +29456,7 @@
         <v/>
       </c>
       <c r="L117" s="15">
-        <f>IFERROR(IF(OR(T117&lt;&gt;"",J117="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T117="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M117" s="228" t="n"/>
@@ -29497,7 +29497,7 @@
         <v/>
       </c>
       <c r="L118" s="15">
-        <f>IFERROR(IF(OR(T118&lt;&gt;"",J118="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T118="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M118" s="228" t="n"/>
@@ -29538,7 +29538,7 @@
         <v/>
       </c>
       <c r="L119" s="15">
-        <f>IFERROR(IF(OR(T119&lt;&gt;"",J119="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T119="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M119" s="228" t="n"/>
@@ -29579,7 +29579,7 @@
         <v/>
       </c>
       <c r="L120" s="15">
-        <f>IFERROR(IF(OR(T120&lt;&gt;"",J120="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T120="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M120" s="228" t="n"/>
@@ -29620,7 +29620,7 @@
         <v/>
       </c>
       <c r="L121" s="15">
-        <f>IFERROR(IF(OR(T121&lt;&gt;"",J121="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T121="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M121" s="228" t="n"/>
@@ -29661,7 +29661,7 @@
         <v/>
       </c>
       <c r="L122" s="15">
-        <f>IFERROR(IF(OR(T122&lt;&gt;"",J122="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T122="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M122" s="228" t="n"/>
@@ -29702,7 +29702,7 @@
         <v/>
       </c>
       <c r="L123" s="15">
-        <f>IFERROR(IF(OR(T123&lt;&gt;"",J123="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T123="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M123" s="228" t="n"/>
@@ -29743,7 +29743,7 @@
         <v/>
       </c>
       <c r="L124" s="15">
-        <f>IFERROR(IF(OR(T124&lt;&gt;"",J124="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T124="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M124" s="228" t="n"/>
@@ -29784,7 +29784,7 @@
         <v/>
       </c>
       <c r="L125" s="15">
-        <f>IFERROR(IF(OR(T125&lt;&gt;"",J125="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T125="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M125" s="228" t="n"/>
@@ -29825,7 +29825,7 @@
         <v/>
       </c>
       <c r="L126" s="15">
-        <f>IFERROR(IF(OR(T126&lt;&gt;"",J126="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T126="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M126" s="228" t="n"/>
@@ -29866,7 +29866,7 @@
         <v/>
       </c>
       <c r="L127" s="15">
-        <f>IFERROR(IF(OR(T127&lt;&gt;"",J127="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T127="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M127" s="228" t="n"/>
@@ -29907,7 +29907,7 @@
         <v/>
       </c>
       <c r="L128" s="15">
-        <f>IFERROR(IF(OR(T128&lt;&gt;"",J128="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T128="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M128" s="228" t="n"/>
@@ -29948,7 +29948,7 @@
         <v/>
       </c>
       <c r="L129" s="15">
-        <f>IFERROR(IF(OR(T129&lt;&gt;"",J129="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T129="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M129" s="228" t="n"/>
@@ -29989,7 +29989,7 @@
         <v/>
       </c>
       <c r="L130" s="15">
-        <f>IFERROR(IF(OR(T130&lt;&gt;"",J130="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T130="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M130" s="228" t="n"/>
@@ -30030,7 +30030,7 @@
         <v/>
       </c>
       <c r="L131" s="15">
-        <f>IFERROR(IF(OR(T131&lt;&gt;"",J131="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T131="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M131" s="228" t="n"/>
@@ -30071,7 +30071,7 @@
         <v/>
       </c>
       <c r="L132" s="15">
-        <f>IFERROR(IF(OR(T132&lt;&gt;"",J132="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T132="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M132" s="228" t="n"/>
@@ -30112,7 +30112,7 @@
         <v/>
       </c>
       <c r="L133" s="15">
-        <f>IFERROR(IF(OR(T133&lt;&gt;"",J133="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T133="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M133" s="228" t="n"/>
@@ -30153,7 +30153,7 @@
         <v/>
       </c>
       <c r="L134" s="15">
-        <f>IFERROR(IF(OR(T134&lt;&gt;"",J134="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T134="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M134" s="228" t="n"/>
@@ -30194,7 +30194,7 @@
         <v/>
       </c>
       <c r="L135" s="15">
-        <f>IFERROR(IF(OR(T135&lt;&gt;"",J135="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T135="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M135" s="228" t="n"/>
@@ -30235,7 +30235,7 @@
         <v/>
       </c>
       <c r="L136" s="15">
-        <f>IFERROR(IF(OR(T136&lt;&gt;"",J136="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T136="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M136" s="228" t="n"/>
@@ -30276,7 +30276,7 @@
         <v/>
       </c>
       <c r="L137" s="15">
-        <f>IFERROR(IF(OR(T137&lt;&gt;"",J137="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T137="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M137" s="228" t="n"/>
@@ -30317,7 +30317,7 @@
         <v/>
       </c>
       <c r="L138" s="15">
-        <f>IFERROR(IF(OR(T138&lt;&gt;"",J138="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T138="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M138" s="228" t="n"/>
@@ -30358,7 +30358,7 @@
         <v/>
       </c>
       <c r="L139" s="15">
-        <f>IFERROR(IF(OR(T139&lt;&gt;"",J139="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T139="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M139" s="228" t="n"/>
@@ -30399,7 +30399,7 @@
         <v/>
       </c>
       <c r="L140" s="15">
-        <f>IFERROR(IF(OR(T140&lt;&gt;"",J140="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T140="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M140" s="228" t="n"/>
@@ -30440,7 +30440,7 @@
         <v/>
       </c>
       <c r="L141" s="15">
-        <f>IFERROR(IF(OR(T141&lt;&gt;"",J141="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T141="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M141" s="228" t="n"/>
@@ -30481,7 +30481,7 @@
         <v/>
       </c>
       <c r="L142" s="15">
-        <f>IFERROR(IF(OR(T142&lt;&gt;"",J142="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T142="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M142" s="228" t="n"/>
@@ -30522,7 +30522,7 @@
         <v/>
       </c>
       <c r="L143" s="15">
-        <f>IFERROR(IF(OR(T143&lt;&gt;"",J143="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T143="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M143" s="228" t="n"/>
@@ -30563,7 +30563,7 @@
         <v/>
       </c>
       <c r="L144" s="15">
-        <f>IFERROR(IF(OR(T144&lt;&gt;"",J144="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T144="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M144" s="228" t="n"/>
@@ -30604,7 +30604,7 @@
         <v/>
       </c>
       <c r="L145" s="15">
-        <f>IFERROR(IF(OR(T145&lt;&gt;"",J145="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T145="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M145" s="228" t="n"/>
@@ -30645,7 +30645,7 @@
         <v/>
       </c>
       <c r="L146" s="15">
-        <f>IFERROR(IF(OR(T146&lt;&gt;"",J146="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T146="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M146" s="228" t="n"/>
@@ -30686,7 +30686,7 @@
         <v/>
       </c>
       <c r="L147" s="15">
-        <f>IFERROR(IF(OR(T147&lt;&gt;"",J147="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T147="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M147" s="228" t="n"/>
@@ -30727,7 +30727,7 @@
         <v/>
       </c>
       <c r="L148" s="15">
-        <f>IFERROR(IF(OR(T148&lt;&gt;"",J148="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T148="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M148" s="228" t="n"/>
@@ -30768,7 +30768,7 @@
         <v/>
       </c>
       <c r="L149" s="15">
-        <f>IFERROR(IF(OR(T149&lt;&gt;"",J149="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T149="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M149" s="228" t="n"/>
@@ -30809,7 +30809,7 @@
         <v/>
       </c>
       <c r="L150" s="15">
-        <f>IFERROR(IF(OR(T150&lt;&gt;"",J150="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T150="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M150" s="228" t="n"/>
@@ -30850,7 +30850,7 @@
         <v/>
       </c>
       <c r="L151" s="15">
-        <f>IFERROR(IF(OR(T151&lt;&gt;"",J151="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T151="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M151" s="228" t="n"/>
@@ -30891,7 +30891,7 @@
         <v/>
       </c>
       <c r="L152" s="15">
-        <f>IFERROR(IF(OR(T152&lt;&gt;"",J152="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T152="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M152" s="228" t="n"/>
@@ -30932,7 +30932,7 @@
         <v/>
       </c>
       <c r="L153" s="15">
-        <f>IFERROR(IF(OR(T153&lt;&gt;"",J153="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T153="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M153" s="228" t="n"/>
@@ -30973,7 +30973,7 @@
         <v/>
       </c>
       <c r="L154" s="15">
-        <f>IFERROR(IF(OR(T154&lt;&gt;"",J154="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T154="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M154" s="228" t="n"/>
@@ -31014,7 +31014,7 @@
         <v/>
       </c>
       <c r="L155" s="15">
-        <f>IFERROR(IF(OR(T155&lt;&gt;"",J155="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T155="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M155" s="228" t="n"/>
@@ -31055,7 +31055,7 @@
         <v/>
       </c>
       <c r="L156" s="15">
-        <f>IFERROR(IF(OR(T156&lt;&gt;"",J156="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T156="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M156" s="228" t="n"/>
@@ -31096,7 +31096,7 @@
         <v/>
       </c>
       <c r="L157" s="15">
-        <f>IFERROR(IF(OR(T157&lt;&gt;"",J157="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T157="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M157" s="228" t="n"/>
@@ -31137,7 +31137,7 @@
         <v/>
       </c>
       <c r="L158" s="15">
-        <f>IFERROR(IF(OR(T158&lt;&gt;"",J158="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T158="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M158" s="228" t="n"/>
@@ -31178,7 +31178,7 @@
         <v/>
       </c>
       <c r="L159" s="15">
-        <f>IFERROR(IF(OR(T159&lt;&gt;"",J159="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T159="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M159" s="228" t="n"/>
@@ -31219,7 +31219,7 @@
         <v/>
       </c>
       <c r="L160" s="15">
-        <f>IFERROR(IF(OR(T160&lt;&gt;"",J160="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T160="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M160" s="228" t="n"/>
@@ -31260,7 +31260,7 @@
         <v/>
       </c>
       <c r="L161" s="15">
-        <f>IFERROR(IF(OR(T161&lt;&gt;"",J161="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T161="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M161" s="228" t="n"/>
@@ -31301,7 +31301,7 @@
         <v/>
       </c>
       <c r="L162" s="15">
-        <f>IFERROR(IF(OR(T162&lt;&gt;"",J162="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T162="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M162" s="228" t="n"/>
@@ -31342,7 +31342,7 @@
         <v/>
       </c>
       <c r="L163" s="15">
-        <f>IFERROR(IF(OR(T163&lt;&gt;"",J163="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T163="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M163" s="228" t="n"/>
@@ -31383,7 +31383,7 @@
         <v/>
       </c>
       <c r="L164" s="15">
-        <f>IFERROR(IF(OR(T164&lt;&gt;"",J164="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T164="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M164" s="228" t="n"/>
@@ -31424,7 +31424,7 @@
         <v/>
       </c>
       <c r="L165" s="15">
-        <f>IFERROR(IF(OR(T165&lt;&gt;"",J165="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T165="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M165" s="228" t="n"/>
@@ -31465,7 +31465,7 @@
         <v/>
       </c>
       <c r="L166" s="15">
-        <f>IFERROR(IF(OR(T166&lt;&gt;"",J166="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T166="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M166" s="228" t="n"/>
@@ -31506,7 +31506,7 @@
         <v/>
       </c>
       <c r="L167" s="15">
-        <f>IFERROR(IF(OR(T167&lt;&gt;"",J167="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T167="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M167" s="228" t="n"/>
@@ -31547,7 +31547,7 @@
         <v/>
       </c>
       <c r="L168" s="15">
-        <f>IFERROR(IF(OR(T168&lt;&gt;"",J168="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T168="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M168" s="228" t="n"/>
@@ -31588,7 +31588,7 @@
         <v/>
       </c>
       <c r="L169" s="15">
-        <f>IFERROR(IF(OR(T169&lt;&gt;"",J169="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T169="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M169" s="228" t="n"/>
@@ -31629,7 +31629,7 @@
         <v/>
       </c>
       <c r="L170" s="15">
-        <f>IFERROR(IF(OR(T170&lt;&gt;"",J170="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T170="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M170" s="228" t="n"/>
@@ -31670,7 +31670,7 @@
         <v/>
       </c>
       <c r="L171" s="15">
-        <f>IFERROR(IF(OR(T171&lt;&gt;"",J171="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T171="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M171" s="228" t="n"/>
@@ -31711,7 +31711,7 @@
         <v/>
       </c>
       <c r="L172" s="15">
-        <f>IFERROR(IF(OR(T172&lt;&gt;"",J172="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T172="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M172" s="228" t="n"/>
@@ -31752,7 +31752,7 @@
         <v/>
       </c>
       <c r="L173" s="15">
-        <f>IFERROR(IF(OR(T173&lt;&gt;"",J173="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T173="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M173" s="228" t="n"/>
@@ -31793,7 +31793,7 @@
         <v/>
       </c>
       <c r="L174" s="15">
-        <f>IFERROR(IF(OR(T174&lt;&gt;"",J174="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T174="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M174" s="228" t="n"/>
@@ -31834,7 +31834,7 @@
         <v/>
       </c>
       <c r="L175" s="15">
-        <f>IFERROR(IF(OR(T175&lt;&gt;"",J175="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T175="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M175" s="228" t="n"/>
@@ -31875,7 +31875,7 @@
         <v/>
       </c>
       <c r="L176" s="15">
-        <f>IFERROR(IF(OR(T176&lt;&gt;"",J176="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T176="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M176" s="228" t="n"/>
@@ -31916,7 +31916,7 @@
         <v/>
       </c>
       <c r="L177" s="15">
-        <f>IFERROR(IF(OR(T177&lt;&gt;"",J177="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T177="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M177" s="228" t="n"/>
@@ -31957,7 +31957,7 @@
         <v/>
       </c>
       <c r="L178" s="15">
-        <f>IFERROR(IF(OR(T178&lt;&gt;"",J178="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T178="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M178" s="228" t="n"/>
@@ -31998,7 +31998,7 @@
         <v/>
       </c>
       <c r="L179" s="15">
-        <f>IFERROR(IF(OR(T179&lt;&gt;"",J179="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T179="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M179" s="228" t="n"/>
@@ -32039,7 +32039,7 @@
         <v/>
       </c>
       <c r="L180" s="15">
-        <f>IFERROR(IF(OR(T180&lt;&gt;"",J180="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T180="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M180" s="228" t="n"/>
@@ -32080,7 +32080,7 @@
         <v/>
       </c>
       <c r="L181" s="15">
-        <f>IFERROR(IF(OR(T181&lt;&gt;"",J181="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T181="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M181" s="228" t="n"/>
@@ -32121,7 +32121,7 @@
         <v/>
       </c>
       <c r="L182" s="15">
-        <f>IFERROR(IF(OR(T182&lt;&gt;"",J182="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T182="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M182" s="228" t="n"/>
@@ -32162,7 +32162,7 @@
         <v/>
       </c>
       <c r="L183" s="15">
-        <f>IFERROR(IF(OR(T183&lt;&gt;"",J183="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T183="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M183" s="228" t="n"/>
@@ -32203,7 +32203,7 @@
         <v/>
       </c>
       <c r="L184" s="15">
-        <f>IFERROR(IF(OR(T184&lt;&gt;"",J184="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T184="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M184" s="228" t="n"/>
@@ -32244,7 +32244,7 @@
         <v/>
       </c>
       <c r="L185" s="15">
-        <f>IFERROR(IF(OR(T185&lt;&gt;"",J185="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T185="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M185" s="228" t="n"/>
@@ -32285,7 +32285,7 @@
         <v/>
       </c>
       <c r="L186" s="15">
-        <f>IFERROR(IF(OR(T186&lt;&gt;"",J186="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T186="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M186" s="228" t="n"/>
@@ -32326,7 +32326,7 @@
         <v/>
       </c>
       <c r="L187" s="15">
-        <f>IFERROR(IF(OR(T187&lt;&gt;"",J187="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T187="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M187" s="228" t="n"/>
@@ -32367,7 +32367,7 @@
         <v/>
       </c>
       <c r="L188" s="15">
-        <f>IFERROR(IF(OR(T188&lt;&gt;"",J188="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T188="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M188" s="228" t="n"/>
@@ -32408,7 +32408,7 @@
         <v/>
       </c>
       <c r="L189" s="15">
-        <f>IFERROR(IF(OR(T189&lt;&gt;"",J189="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T189="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M189" s="228" t="n"/>
@@ -32449,7 +32449,7 @@
         <v/>
       </c>
       <c r="L190" s="15">
-        <f>IFERROR(IF(OR(T190&lt;&gt;"",J190="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T190="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M190" s="228" t="n"/>
@@ -32490,7 +32490,7 @@
         <v/>
       </c>
       <c r="L191" s="15">
-        <f>IFERROR(IF(OR(T191&lt;&gt;"",J191="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T191="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M191" s="228" t="n"/>
@@ -32531,7 +32531,7 @@
         <v/>
       </c>
       <c r="L192" s="15">
-        <f>IFERROR(IF(OR(T192&lt;&gt;"",J192="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T192="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M192" s="228" t="n"/>
@@ -32572,7 +32572,7 @@
         <v/>
       </c>
       <c r="L193" s="15">
-        <f>IFERROR(IF(OR(T193&lt;&gt;"",J193="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T193="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M193" s="228" t="n"/>
@@ -32613,7 +32613,7 @@
         <v/>
       </c>
       <c r="L194" s="15">
-        <f>IFERROR(IF(OR(T194&lt;&gt;"",J194="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T194="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M194" s="228" t="n"/>
@@ -32654,7 +32654,7 @@
         <v/>
       </c>
       <c r="L195" s="15">
-        <f>IFERROR(IF(OR(T195&lt;&gt;"",J195="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T195="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M195" s="228" t="n"/>
@@ -32695,7 +32695,7 @@
         <v/>
       </c>
       <c r="L196" s="15">
-        <f>IFERROR(IF(OR(T196&lt;&gt;"",J196="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T196="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M196" s="228" t="n"/>
@@ -32736,7 +32736,7 @@
         <v/>
       </c>
       <c r="L197" s="15">
-        <f>IFERROR(IF(OR(T197&lt;&gt;"",J197="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T197="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M197" s="228" t="n"/>
@@ -32777,7 +32777,7 @@
         <v/>
       </c>
       <c r="L198" s="15">
-        <f>IFERROR(IF(OR(T198&lt;&gt;"",J198="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T198="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M198" s="228" t="n"/>
@@ -32818,7 +32818,7 @@
         <v/>
       </c>
       <c r="L199" s="15">
-        <f>IFERROR(IF(OR(T199&lt;&gt;"",J199="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T199="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M199" s="228" t="n"/>
@@ -32859,7 +32859,7 @@
         <v/>
       </c>
       <c r="L200" s="15">
-        <f>IFERROR(IF(OR(T200&lt;&gt;"",J200="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T200="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M200" s="228" t="n"/>
@@ -32900,7 +32900,7 @@
         <v/>
       </c>
       <c r="L201" s="15">
-        <f>IFERROR(IF(OR(T201&lt;&gt;"",J201="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T201="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M201" s="228" t="n"/>
@@ -32941,7 +32941,7 @@
         <v/>
       </c>
       <c r="L202" s="15">
-        <f>IFERROR(IF(OR(T202&lt;&gt;"",J202="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T202="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M202" s="228" t="n"/>
@@ -32982,7 +32982,7 @@
         <v/>
       </c>
       <c r="L203" s="15">
-        <f>IFERROR(IF(OR(T203&lt;&gt;"",J203="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T203="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M203" s="228" t="n"/>
@@ -33023,7 +33023,7 @@
         <v/>
       </c>
       <c r="L204" s="15">
-        <f>IFERROR(IF(OR(T204&lt;&gt;"",J204="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T204="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M204" s="228" t="n"/>
@@ -33064,7 +33064,7 @@
         <v/>
       </c>
       <c r="L205" s="15">
-        <f>IFERROR(IF(OR(T205&lt;&gt;"",J205="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T205="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M205" s="228" t="n"/>
@@ -33105,7 +33105,7 @@
         <v/>
       </c>
       <c r="L206" s="15">
-        <f>IFERROR(IF(OR(T206&lt;&gt;"",J206="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T206="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M206" s="228" t="n"/>
@@ -33146,7 +33146,7 @@
         <v/>
       </c>
       <c r="L207" s="15">
-        <f>IFERROR(IF(OR(T207&lt;&gt;"",J207="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T207="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M207" s="228" t="n"/>
@@ -33187,7 +33187,7 @@
         <v/>
       </c>
       <c r="L208" s="15">
-        <f>IFERROR(IF(OR(T208&lt;&gt;"",J208="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T208="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M208" s="228" t="n"/>
@@ -33228,7 +33228,7 @@
         <v/>
       </c>
       <c r="L209" s="15">
-        <f>IFERROR(IF(OR(T209&lt;&gt;"",J209="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T209="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M209" s="228" t="n"/>
@@ -33269,7 +33269,7 @@
         <v/>
       </c>
       <c r="L210" s="15">
-        <f>IFERROR(IF(OR(T210&lt;&gt;"",J210="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T210="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M210" s="228" t="n"/>
@@ -33310,7 +33310,7 @@
         <v/>
       </c>
       <c r="L211" s="15">
-        <f>IFERROR(IF(OR(T211&lt;&gt;"",J211="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T211="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M211" s="228" t="n"/>
@@ -33351,7 +33351,7 @@
         <v/>
       </c>
       <c r="L212" s="15">
-        <f>IFERROR(IF(OR(T212&lt;&gt;"",J212="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T212="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M212" s="228" t="n"/>
@@ -33392,7 +33392,7 @@
         <v/>
       </c>
       <c r="L213" s="15">
-        <f>IFERROR(IF(OR(T213&lt;&gt;"",J213="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T213="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M213" s="228" t="n"/>
@@ -33433,7 +33433,7 @@
         <v/>
       </c>
       <c r="L214" s="15">
-        <f>IFERROR(IF(OR(T214&lt;&gt;"",J214="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T214="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M214" s="228" t="n"/>
@@ -33474,7 +33474,7 @@
         <v/>
       </c>
       <c r="L215" s="15">
-        <f>IFERROR(IF(OR(T215&lt;&gt;"",J215="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T215="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M215" s="228" t="n"/>
@@ -33515,7 +33515,7 @@
         <v/>
       </c>
       <c r="L216" s="15">
-        <f>IFERROR(IF(OR(T216&lt;&gt;"",J216="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T216="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M216" s="228" t="n"/>
@@ -33556,7 +33556,7 @@
         <v/>
       </c>
       <c r="L217" s="15">
-        <f>IFERROR(IF(OR(T217&lt;&gt;"",J217="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T217="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M217" s="228" t="n"/>
@@ -33597,7 +33597,7 @@
         <v/>
       </c>
       <c r="L218" s="15">
-        <f>IFERROR(IF(OR(T218&lt;&gt;"",J218="已移請偵查隊續辦"),"否","是"),"是")</f>
+        <f>IFERROR(IF(T218="","是","否"),"是")</f>
         <v/>
       </c>
       <c r="M218" s="228" t="n"/>
